--- a/5-excel-data-types-and-conversions/starwars.xlsx
+++ b/5-excel-data-types-and-conversions/starwars.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maryvanvalkenburg/NSS/DDA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{5B996D39-A8F4-3241-8F2D-45DFE2E5CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D1F343A-5810-4F05-9D44-2F41E00E4C6E}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="8_{5B996D39-A8F4-3241-8F2D-45DFE2E5CD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E58E7E8-10A6-4B3D-B167-29F93A856559}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2260" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="2260" windowWidth="28040" windowHeight="17440" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="starwars" sheetId="1" r:id="rId1"/>
     <sheet name="data_dictionary" sheetId="2" r:id="rId2"/>
     <sheet name="excercises" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="chapter1">excercises!$A$1:$A$1</definedName>
+    <definedName name="chapter3">excercises!$A$7:$A$7</definedName>
+    <definedName name="chapter5">excercises!$A$14:$A$14</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="311">
   <si>
     <t>name</t>
   </si>
@@ -68,12 +73,18 @@
     <t>height</t>
   </si>
   <si>
+    <t>height_inches</t>
+  </si>
+  <si>
     <t>height_m</t>
   </si>
   <si>
     <t>mass</t>
   </si>
   <si>
+    <t>weight</t>
+  </si>
+  <si>
     <t>BMI</t>
   </si>
   <si>
@@ -95,6 +106,9 @@
     <t>age</t>
   </si>
   <si>
+    <t>age_number_check</t>
+  </si>
+  <si>
     <t>age_days</t>
   </si>
   <si>
@@ -881,15 +895,12 @@
     <t>question</t>
   </si>
   <si>
-    <t>answers</t>
+    <t>answer</t>
   </si>
   <si>
     <t>Review the data dictionary. Identify the units of the height and weight columns.</t>
   </si>
   <si>
-    <t>cm,kg</t>
-  </si>
-  <si>
     <t>Locate Biggs Darklighter’s age. Note the cell address.</t>
   </si>
   <si>
@@ -917,40 +928,79 @@
     <t>chapter 3</t>
   </si>
   <si>
+    <t>1.</t>
+  </si>
+  <si>
     <t>Create a BMI_rank column, then write a formula to rank each BMI.</t>
   </si>
   <si>
     <t>=RANK($E2,$E$2:$E$88)</t>
   </si>
   <si>
+    <t>2.</t>
+  </si>
+  <si>
     <t>Redo the BMI column using multiple IF statements to output 0 if height or weight is NA.</t>
   </si>
   <si>
     <t>=IF(OR($D2="NA",$B2="NA"),0,$D2/($C2^2))</t>
   </si>
   <si>
+    <t>3.</t>
+  </si>
+  <si>
     <t>Calculate the average BMI for values that aren’t 0.</t>
   </si>
   <si>
+    <t>4.</t>
+  </si>
+  <si>
     <t>Add an age in days column and another column called birthdate.</t>
   </si>
   <si>
     <t>=$K2*365</t>
   </si>
   <si>
+    <t>5.</t>
+  </si>
+  <si>
     <t>Use a lookup function to find the character closest in age to you.</t>
   </si>
   <si>
     <t>IG-88 (5475=VLOOKUP(DAYS(TODAY(),DATE(1995,3,7)),L2:L88,1))</t>
   </si>
   <si>
-    <t>Bonus</t>
+    <t>Bonus:</t>
   </si>
   <si>
     <t>Add a first_movie column containing just the first movie listed for each character.</t>
   </si>
   <si>
     <t>=INDEX(TEXTSPLIT($Q2,{","," "}),1)</t>
+  </si>
+  <si>
+    <t>chapter 5</t>
+  </si>
+  <si>
+    <t>Data Type Check:
+Insert a column to the right of the age column, name it age_number_check, and write a formula to check if the values in the age column are numbers.</t>
+  </si>
+  <si>
+    <t>=ISNUMBER(K2)</t>
+  </si>
+  <si>
+    <t>Height Conversion:
+Insert a column to the right of the height column, name it height_inches, and write a formula to convert height from centimeters to inches, rounding down to the nearest half-inch.</t>
+  </si>
+  <si>
+    <t>=FLOOR(CONVERT(B2,"cm","in"),0.5)</t>
+  </si>
+  <si>
+    <t>Mass Conversion:
+Insert a column to the right of the mass column, name it weight, and write a formula to convert mass in kilograms to weight in pounds. Round this to the nearest quarter-pound. (Hint: Find Jabba the Hutt’s weight in pounds.)</t>
+  </si>
+  <si>
+    <t>=FLOOR(CONVERT(E2,"kg","lbm"),0.25)</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1160,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1290,6 +1340,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1451,7 +1507,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1459,13 +1515,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment textRotation="45"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1522,6 +1593,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1821,25 +1909,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:T89"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="7" width="9.25" customWidth="1"/>
-    <col min="15" max="15" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="125.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="11.125" customWidth="1"/>
+    <col min="5" max="9" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
+    <col min="20" max="20" width="125.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="32.25">
+    <row r="1" spans="1:20" ht="32.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1848,16 +1939,16 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1872,7 +1963,7 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
@@ -1884,4884 +1975,5937 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="32.25">
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="32.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>172</v>
       </c>
       <c r="C2">
+        <f>FLOOR(CONVERT(B2,"cm","in"),0.5)</f>
+        <v>67.5</v>
+      </c>
+      <c r="D2">
         <f>$B2/100</f>
         <v>1.72</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>77</v>
       </c>
-      <c r="E2" s="4">
-        <f>IF(OR($D2="NA",$B2="NA"),0,$D2/($C2^2))</f>
+      <c r="F2">
+        <f>FLOOR(CONVERT(E2,"kg","lbm"),0.25)</f>
+        <v>169.75</v>
+      </c>
+      <c r="G2" s="4">
+        <f>IF(OR($E2="NA",$B2="NA"),0,$E2/($D2^2))</f>
         <v>26.027582477014604</v>
       </c>
-      <c r="F2" s="4">
-        <f>$E2-$E$5</f>
+      <c r="H2" s="4">
+        <f>$G2-$G$5</f>
         <v>-7.302483202820703</v>
       </c>
-      <c r="G2" s="4">
-        <f>RANK($E2,$E$2:$E$88)</f>
+      <c r="I2" s="4">
+        <f>RANK($G2,$G$2:$G$88)</f>
         <v>18</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2">
-        <v>19</v>
-      </c>
-      <c r="L2">
-        <f>$K2*365</f>
+      <c r="N2" t="b">
+        <f>ISNUMBER(M2)</f>
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <f>$M2*365</f>
         <v>6935</v>
       </c>
-      <c r="M2">
-        <f ca="1">VLOOKUP(_xlfn.DAYS(TODAY(),DATE(1995,3,7)),L2:L88,1)</f>
+      <c r="P2">
+        <f ca="1">VLOOKUP(_xlfn.DAYS(TODAY(),DATE(1995,3,7)),O2:O88,1)</f>
         <v>5475</v>
       </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="4" t="str" cm="1">
-        <f t="array" ref="P2">INDEX(_xlfn.TEXTSPLIT($Q2,{","," "}),1)</f>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="4" t="str" cm="1">
+        <f t="array" ref="S2">INDEX(_xlfn.TEXTSPLIT($T2,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="32.25">
+      <c r="T2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="32.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>167</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C66" si="0">$B3/100</f>
+        <f t="shared" ref="C3:C66" si="0">FLOOR(CONVERT(B3,"cm","in"),0.5)</f>
+        <v>65.5</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D66" si="1">$B3/100</f>
         <v>1.67</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>75</v>
       </c>
-      <c r="E3" s="4">
-        <f t="shared" ref="E3:E66" si="1">IF(OR($D3="NA",$B3="NA"),0,$D3/($C3^2))</f>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="2">FLOOR(CONVERT(E3,"kg","lbm"),0.25)</f>
+        <v>165.25</v>
+      </c>
+      <c r="G3" s="4">
+        <f>IF(OR($E3="NA",$B3="NA"),0,$E3/($D3^2))</f>
         <v>26.892323138154829</v>
       </c>
-      <c r="F3" s="4">
-        <f t="shared" ref="F3:F66" si="2">$E3-$E$5</f>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H66" si="3">$G3-$G$5</f>
         <v>-6.4377425416804783</v>
       </c>
-      <c r="G3" s="4">
-        <f t="shared" ref="G3:G66" si="3">RANK($E3,$E$2:$E$88)</f>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I66" si="4">RANK($G3,$G$2:$G$88)</f>
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
       <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3">
         <v>112</v>
       </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L66" si="4">$K3*365</f>
+      <c r="N3" t="b">
+        <f t="shared" ref="N3:N66" si="5">ISNUMBER(M3)</f>
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O66" si="6">$M3*365</f>
         <v>40880</v>
       </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="4" t="str" cm="1">
-        <f t="array" ref="P3">INDEX(_xlfn.TEXTSPLIT($Q3,{","," "}),1)</f>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="4" t="str" cm="1">
+        <f t="array" ref="S3">INDEX(_xlfn.TEXTSPLIT($T3,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="32.25">
+      <c r="T3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="32.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>96</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
+        <v>37.5</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
         <v>0.96</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>32</v>
       </c>
-      <c r="E4" s="4">
-        <f t="shared" si="1"/>
+      <c r="F4">
+        <f t="shared" si="2"/>
+        <v>70.5</v>
+      </c>
+      <c r="G4" s="4">
+        <f>IF(OR($E4="NA",$B4="NA"),0,$E4/($D4^2))</f>
         <v>34.722222222222221</v>
       </c>
-      <c r="F4" s="4">
-        <f t="shared" si="2"/>
+      <c r="H4" s="4">
+        <f t="shared" si="3"/>
         <v>1.392156542386914</v>
       </c>
-      <c r="G4" s="4">
-        <f t="shared" si="3"/>
+      <c r="I4" s="4">
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4">
+        <v>33</v>
+      </c>
+      <c r="N4" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="6"/>
+        <v>12045</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4">
-        <v>33</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="4"/>
-        <v>12045</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="4" t="str" cm="1">
-        <f t="array" ref="P4">INDEX(_xlfn.TEXTSPLIT($Q4,{","," "}),1)</f>
+      <c r="S4" s="4" t="str" cm="1">
+        <f t="array" ref="S4">INDEX(_xlfn.TEXTSPLIT($T4,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="32.25">
+      <c r="T4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="32.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>202</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
+        <v>79.5</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
         <v>2.02</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>136</v>
       </c>
-      <c r="E5" s="4">
-        <f t="shared" si="1"/>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>299.75</v>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(OR($E5="NA",$B5="NA"),0,$E5/($D5^2))</f>
         <v>33.330065679835307</v>
       </c>
-      <c r="F5" s="4">
-        <f>$E5-$E$5</f>
+      <c r="H5" s="4">
+        <f>$G5-$G$5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="4">
-        <f t="shared" si="3"/>
+      <c r="I5" s="4">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
       <c r="J5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
         <v>41.9</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="4"/>
+      <c r="N5" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="6"/>
         <v>15293.5</v>
       </c>
-      <c r="N5" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="4" t="str" cm="1">
-        <f t="array" ref="P5">INDEX(_xlfn.TEXTSPLIT($Q5,{","," "}),1)</f>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="4" t="str" cm="1">
+        <f t="array" ref="S5">INDEX(_xlfn.TEXTSPLIT($T5,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="32.25">
+      <c r="T5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="32.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>150</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>49</v>
       </c>
-      <c r="E6" s="4">
-        <f t="shared" si="1"/>
+      <c r="F6">
+        <f t="shared" si="2"/>
+        <v>108</v>
+      </c>
+      <c r="G6" s="4">
+        <f>IF(OR($E6="NA",$B6="NA"),0,$E6/($D6^2))</f>
         <v>21.777777777777779</v>
       </c>
-      <c r="F6" s="4">
-        <f t="shared" si="2"/>
+      <c r="H6" s="4">
+        <f t="shared" si="3"/>
         <v>-11.552287902057529</v>
       </c>
-      <c r="G6" s="4">
-        <f t="shared" si="3"/>
+      <c r="I6" s="4">
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
-      <c r="H6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
       <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6">
         <v>19</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="4"/>
+      <c r="N6" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="6"/>
         <v>6935</v>
       </c>
-      <c r="N6" t="s">
-        <v>42</v>
-      </c>
-      <c r="O6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P6" s="4" t="str" cm="1">
-        <f t="array" ref="P6">INDEX(_xlfn.TEXTSPLIT($Q6,{","," "}),1)</f>
+      <c r="Q6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S6" s="4" t="str" cm="1">
+        <f t="array" ref="S6">INDEX(_xlfn.TEXTSPLIT($T6,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="32.25">
+      <c r="T6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="32.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>178</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>120</v>
       </c>
-      <c r="E7" s="4">
-        <f t="shared" si="1"/>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>264.5</v>
+      </c>
+      <c r="G7" s="4">
+        <f>IF(OR($E7="NA",$B7="NA"),0,$E7/($D7^2))</f>
         <v>37.874005807347558</v>
       </c>
-      <c r="F7" s="4">
-        <f t="shared" si="2"/>
+      <c r="H7" s="4">
+        <f t="shared" si="3"/>
         <v>4.5439401275122506</v>
       </c>
-      <c r="G7" s="4">
-        <f t="shared" si="3"/>
+      <c r="I7" s="4">
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
       <c r="J7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7">
         <v>52</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="4"/>
+      <c r="N7" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="6"/>
         <v>18980</v>
       </c>
-      <c r="N7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="4" t="str" cm="1">
-        <f t="array" ref="P7">INDEX(_xlfn.TEXTSPLIT($Q7,{","," "}),1)</f>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="4" t="str" cm="1">
+        <f t="array" ref="S7">INDEX(_xlfn.TEXTSPLIT($T7,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="32.25">
+      <c r="T7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="32.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B8">
         <v>165</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
+        <v>64.5</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
         <v>1.65</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>75</v>
       </c>
-      <c r="E8" s="4">
-        <f t="shared" si="1"/>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>165.25</v>
+      </c>
+      <c r="G8" s="4">
+        <f>IF(OR($E8="NA",$B8="NA"),0,$E8/($D8^2))</f>
         <v>27.548209366391188</v>
       </c>
-      <c r="F8" s="4">
-        <f t="shared" si="2"/>
+      <c r="H8" s="4">
+        <f t="shared" si="3"/>
         <v>-5.7818563134441199</v>
       </c>
-      <c r="G8" s="4">
-        <f t="shared" si="3"/>
+      <c r="I8" s="4">
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="H8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
       <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8">
         <v>47</v>
       </c>
-      <c r="L8">
-        <f t="shared" si="4"/>
+      <c r="N8" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="6"/>
         <v>17155</v>
       </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P8" s="4" t="str" cm="1">
-        <f t="array" ref="P8">INDEX(_xlfn.TEXTSPLIT($Q8,{","," "}),1)</f>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="4" t="str" cm="1">
+        <f t="array" ref="S8">INDEX(_xlfn.TEXTSPLIT($T8,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="32.25">
+      <c r="T8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="16.5">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B9">
         <v>97</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
         <v>0.97</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>32</v>
       </c>
-      <c r="E9" s="4">
-        <f t="shared" si="1"/>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>70.5</v>
+      </c>
+      <c r="G9" s="4">
+        <f>IF(OR($E9="NA",$B9="NA"),0,$E9/($D9^2))</f>
         <v>34.009990434690195</v>
       </c>
-      <c r="F9" s="4">
-        <f t="shared" si="2"/>
+      <c r="H9" s="4">
+        <f t="shared" si="3"/>
         <v>0.67992475485488768</v>
       </c>
-      <c r="G9" s="4">
-        <f t="shared" si="3"/>
+      <c r="I9" s="4">
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" t="s">
-        <v>49</v>
-      </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N9" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" s="4" t="str" cm="1">
-        <f t="array" ref="P9">INDEX(_xlfn.TEXTSPLIT($Q9,{","," "}),1)</f>
+        <v>52</v>
+      </c>
+      <c r="L9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" s="4" t="str" cm="1">
+        <f t="array" ref="S9">INDEX(_xlfn.TEXTSPLIT($T9,{","," "}),1)</f>
         <v>A New Hope</v>
       </c>
-      <c r="Q9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="32.25">
+      <c r="T9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="16.5">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>183</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>84</v>
       </c>
-      <c r="E10" s="4">
-        <f t="shared" si="1"/>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="G10" s="4">
+        <f>IF(OR($E10="NA",$B10="NA"),0,$E10/($D10^2))</f>
         <v>25.082863029651524</v>
       </c>
-      <c r="F10" s="4">
-        <f t="shared" si="2"/>
+      <c r="H10" s="4">
+        <f t="shared" si="3"/>
         <v>-8.2472026501837838</v>
       </c>
-      <c r="G10" s="4">
-        <f t="shared" si="3"/>
+      <c r="I10" s="4">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="H10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
       <c r="J10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10">
+        <v>55</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
         <v>24</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="4"/>
+      <c r="N10" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="6"/>
         <v>8760</v>
       </c>
-      <c r="N10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="4" t="str" cm="1">
-        <f t="array" ref="P10">INDEX(_xlfn.TEXTSPLIT($Q10,{","," "}),1)</f>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="4" t="str" cm="1">
+        <f t="array" ref="S10">INDEX(_xlfn.TEXTSPLIT($T10,{","," "}),1)</f>
         <v>A New Hope</v>
       </c>
-      <c r="Q10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="32.25">
+      <c r="T10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="32.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <v>182</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
+        <v>71.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
         <v>1.82</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>77</v>
       </c>
-      <c r="E11" s="4">
-        <f t="shared" si="1"/>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>169.75</v>
+      </c>
+      <c r="G11" s="4">
+        <f>IF(OR($E11="NA",$B11="NA"),0,$E11/($D11^2))</f>
         <v>23.245984784446321</v>
       </c>
-      <c r="F11" s="4">
-        <f t="shared" si="2"/>
+      <c r="H11" s="4">
+        <f t="shared" si="3"/>
         <v>-10.084080895388986</v>
       </c>
-      <c r="G11" s="4">
-        <f t="shared" si="3"/>
+      <c r="I11" s="4">
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
-      <c r="H11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
       <c r="J11" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11">
         <v>57</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="4"/>
+      <c r="K11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11">
+        <v>57</v>
+      </c>
+      <c r="N11" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="6"/>
         <v>20805</v>
       </c>
-      <c r="N11" t="s">
-        <v>56</v>
-      </c>
-      <c r="O11" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="4" t="str" cm="1">
-        <f t="array" ref="P11">INDEX(_xlfn.TEXTSPLIT($Q11,{","," "}),1)</f>
+      <c r="Q11" t="s">
+        <v>59</v>
+      </c>
+      <c r="R11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="4" t="str" cm="1">
+        <f t="array" ref="S11">INDEX(_xlfn.TEXTSPLIT($T11,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="32.25">
+      <c r="T11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="32.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>188</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>84</v>
       </c>
-      <c r="E12" s="4">
-        <f t="shared" si="1"/>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="G12" s="4">
+        <f>IF(OR($E12="NA",$B12="NA"),0,$E12/($D12^2))</f>
         <v>23.766410140334994</v>
       </c>
-      <c r="F12" s="4">
-        <f t="shared" si="2"/>
+      <c r="H12" s="4">
+        <f t="shared" si="3"/>
         <v>-9.5636555395003136</v>
       </c>
-      <c r="G12" s="4">
-        <f t="shared" si="3"/>
+      <c r="I12" s="4">
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" t="s">
-        <v>19</v>
-      </c>
       <c r="J12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12">
         <v>41.9</v>
       </c>
-      <c r="L12">
-        <f t="shared" si="4"/>
+      <c r="N12" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="6"/>
         <v>15293.5</v>
       </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="4" t="str" cm="1">
-        <f t="array" ref="P12">INDEX(_xlfn.TEXTSPLIT($Q12,{","," "}),1)</f>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="4" t="str" cm="1">
+        <f t="array" ref="S12">INDEX(_xlfn.TEXTSPLIT($T12,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="32.25">
+      <c r="T12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="32.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>180</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G13" s="4">
+        <f>IF(OR($E13="NA",$B13="NA"),0,$E13/($D13^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13">
+        <v>64</v>
+      </c>
+      <c r="N13" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="6"/>
+        <v>23360</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>64</v>
+      </c>
+      <c r="R13" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13">
-        <v>64</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="4"/>
-        <v>23360</v>
-      </c>
-      <c r="N13" t="s">
-        <v>61</v>
-      </c>
-      <c r="O13" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="4" t="str" cm="1">
-        <f t="array" ref="P13">INDEX(_xlfn.TEXTSPLIT($Q13,{","," "}),1)</f>
+      <c r="S13" s="4" t="str" cm="1">
+        <f t="array" ref="S13">INDEX(_xlfn.TEXTSPLIT($T13,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="32.25">
+      <c r="T13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="32.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14">
         <v>228</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
+        <v>89.5</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
         <v>2.2799999999999998</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>112</v>
       </c>
-      <c r="E14" s="4">
-        <f t="shared" si="1"/>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>246.75</v>
+      </c>
+      <c r="G14" s="4">
+        <f>IF(OR($E14="NA",$B14="NA"),0,$E14/($D14^2))</f>
         <v>21.545090797168363</v>
       </c>
-      <c r="F14" s="4">
-        <f t="shared" si="2"/>
+      <c r="H14" s="4">
+        <f t="shared" si="3"/>
         <v>-11.784974882666944</v>
       </c>
-      <c r="G14" s="4">
-        <f t="shared" si="3"/>
+      <c r="I14" s="4">
+        <f t="shared" si="4"/>
         <v>44</v>
       </c>
-      <c r="H14" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" t="s">
-        <v>64</v>
-      </c>
       <c r="J14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14">
+        <v>43</v>
+      </c>
+      <c r="K14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14">
         <v>200</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="4"/>
+      <c r="N14" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="6"/>
         <v>73000</v>
       </c>
-      <c r="N14" t="s">
-        <v>65</v>
-      </c>
-      <c r="O14" t="s">
-        <v>66</v>
-      </c>
-      <c r="P14" s="4" t="str" cm="1">
-        <f t="array" ref="P14">INDEX(_xlfn.TEXTSPLIT($Q14,{","," "}),1)</f>
+      <c r="Q14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" t="s">
+        <v>69</v>
+      </c>
+      <c r="S14" s="4" t="str" cm="1">
+        <f t="array" ref="S14">INDEX(_xlfn.TEXTSPLIT($T14,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="32.25">
+      <c r="T14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="32.25">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <v>180</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>80</v>
       </c>
-      <c r="E15" s="4">
-        <f t="shared" si="1"/>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>176.25</v>
+      </c>
+      <c r="G15" s="4">
+        <f>IF(OR($E15="NA",$B15="NA"),0,$E15/($D15^2))</f>
         <v>24.691358024691358</v>
       </c>
-      <c r="F15" s="4">
-        <f t="shared" si="2"/>
+      <c r="H15" s="4">
+        <f t="shared" si="3"/>
         <v>-8.6387076551439499</v>
       </c>
-      <c r="G15" s="4">
-        <f t="shared" si="3"/>
+      <c r="I15" s="4">
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" t="s">
-        <v>19</v>
-      </c>
       <c r="J15" t="s">
-        <v>40</v>
-      </c>
-      <c r="K15">
+        <v>43</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15">
         <v>29</v>
       </c>
-      <c r="L15">
-        <f t="shared" si="4"/>
+      <c r="N15" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="6"/>
         <v>10585</v>
       </c>
-      <c r="N15" t="s">
-        <v>68</v>
-      </c>
-      <c r="O15" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="4" t="str" cm="1">
-        <f t="array" ref="P15">INDEX(_xlfn.TEXTSPLIT($Q15,{","," "}),1)</f>
+      <c r="Q15" t="s">
+        <v>71</v>
+      </c>
+      <c r="R15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" s="4" t="str" cm="1">
+        <f t="array" ref="S15">INDEX(_xlfn.TEXTSPLIT($T15,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="32.25">
+      <c r="T15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="16.5">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B16">
         <v>173</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
         <v>1.73</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>74</v>
       </c>
-      <c r="E16" s="4">
-        <f t="shared" si="1"/>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+      <c r="G16" s="4">
+        <f>IF(OR($E16="NA",$B16="NA"),0,$E16/($D16^2))</f>
         <v>24.725182932941294</v>
       </c>
-      <c r="F16" s="4">
-        <f t="shared" si="2"/>
+      <c r="H16" s="4">
+        <f t="shared" si="3"/>
         <v>-8.6048827468940132</v>
       </c>
-      <c r="G16" s="4">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="H16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" t="s">
-        <v>71</v>
+      <c r="I16" s="4">
+        <f t="shared" si="4"/>
+        <v>28</v>
       </c>
       <c r="J16" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="K16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16">
         <v>44</v>
       </c>
-      <c r="L16">
-        <f t="shared" si="4"/>
+      <c r="N16" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="6"/>
         <v>16060</v>
       </c>
-      <c r="N16" t="s">
-        <v>72</v>
-      </c>
-      <c r="O16" t="s">
-        <v>73</v>
-      </c>
-      <c r="P16" s="4" t="str" cm="1">
-        <f t="array" ref="P16">INDEX(_xlfn.TEXTSPLIT($Q16,{","," "}),1)</f>
+      <c r="Q16" t="s">
+        <v>75</v>
+      </c>
+      <c r="R16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S16" s="4" t="str" cm="1">
+        <f t="array" ref="S16">INDEX(_xlfn.TEXTSPLIT($T16,{","," "}),1)</f>
         <v>A New Hope</v>
       </c>
-      <c r="Q16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="32.25">
+      <c r="T16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="32.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B17">
         <v>175</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>1358</v>
       </c>
-      <c r="E17" s="4">
-        <f t="shared" si="1"/>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>2993.75</v>
+      </c>
+      <c r="G17" s="4">
+        <f>IF(OR($E17="NA",$B17="NA"),0,$E17/($D17^2))</f>
         <v>443.42857142857144</v>
       </c>
-      <c r="F17" s="4">
-        <f t="shared" si="2"/>
+      <c r="H17" s="4">
+        <f t="shared" si="3"/>
         <v>410.09850574873616</v>
       </c>
-      <c r="G17" s="4">
-        <f t="shared" si="3"/>
+      <c r="I17" s="4">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" t="s">
-        <v>75</v>
-      </c>
       <c r="J17" t="s">
-        <v>76</v>
-      </c>
-      <c r="K17">
+        <v>28</v>
+      </c>
+      <c r="K17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L17" t="s">
+        <v>79</v>
+      </c>
+      <c r="M17">
         <v>600</v>
       </c>
-      <c r="L17">
-        <f t="shared" si="4"/>
+      <c r="N17" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="6"/>
         <v>219000</v>
       </c>
-      <c r="N17" t="s">
-        <v>77</v>
-      </c>
-      <c r="O17" t="s">
-        <v>78</v>
-      </c>
-      <c r="P17" s="4" t="str" cm="1">
-        <f t="array" ref="P17">INDEX(_xlfn.TEXTSPLIT($Q17,{","," "}),1)</f>
+      <c r="Q17" t="s">
+        <v>80</v>
+      </c>
+      <c r="R17" t="s">
+        <v>81</v>
+      </c>
+      <c r="S17" s="4" t="str" cm="1">
+        <f t="array" ref="S17">INDEX(_xlfn.TEXTSPLIT($T17,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="32.25">
+      <c r="T17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="32.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B18">
         <v>170</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>77</v>
       </c>
-      <c r="E18" s="4">
-        <f t="shared" si="1"/>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>169.75</v>
+      </c>
+      <c r="G18" s="4">
+        <f>IF(OR($E18="NA",$B18="NA"),0,$E18/($D18^2))</f>
         <v>26.643598615916957</v>
       </c>
-      <c r="F18" s="4">
-        <f t="shared" si="2"/>
+      <c r="H18" s="4">
+        <f t="shared" si="3"/>
         <v>-6.6864670639183501</v>
       </c>
-      <c r="G18" s="4">
-        <f t="shared" si="3"/>
+      <c r="I18" s="4">
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="H18" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" t="s">
-        <v>19</v>
-      </c>
       <c r="J18" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18">
+        <v>43</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>84</v>
+      </c>
+      <c r="M18">
         <v>21</v>
       </c>
-      <c r="L18">
-        <f t="shared" si="4"/>
+      <c r="N18" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="6"/>
         <v>7665</v>
       </c>
-      <c r="N18" t="s">
-        <v>68</v>
-      </c>
-      <c r="O18" t="s">
-        <v>22</v>
-      </c>
-      <c r="P18" s="4" t="str" cm="1">
-        <f t="array" ref="P18">INDEX(_xlfn.TEXTSPLIT($Q18,{","," "}),1)</f>
+      <c r="Q18" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="4" t="str" cm="1">
+        <f t="array" ref="S18">INDEX(_xlfn.TEXTSPLIT($T18,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="32.25">
+      <c r="T18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="16.5">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B19">
         <v>180</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>110</v>
       </c>
-      <c r="E19" s="4">
-        <f t="shared" si="1"/>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>242.5</v>
+      </c>
+      <c r="G19" s="4">
+        <f>IF(OR($E19="NA",$B19="NA"),0,$E19/($D19^2))</f>
         <v>33.950617283950614</v>
       </c>
-      <c r="F19" s="4">
-        <f t="shared" si="2"/>
+      <c r="H19" s="4">
+        <f t="shared" si="3"/>
         <v>0.62055160411530608</v>
       </c>
-      <c r="G19" s="4">
-        <f t="shared" si="3"/>
+      <c r="I19" s="4">
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="H19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O19" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>87</v>
+      </c>
+      <c r="R19" t="s">
         <v>25</v>
       </c>
-      <c r="L19" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N19" t="s">
-        <v>84</v>
-      </c>
-      <c r="O19" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19" s="4" t="str" cm="1">
-        <f t="array" ref="P19">INDEX(_xlfn.TEXTSPLIT($Q19,{","," "}),1)</f>
+      <c r="S19" s="4" t="str" cm="1">
+        <f t="array" ref="S19">INDEX(_xlfn.TEXTSPLIT($T19,{","," "}),1)</f>
         <v>A New Hope</v>
       </c>
-      <c r="Q19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="32.25">
+      <c r="T19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="32.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B20">
         <v>66</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>17</v>
       </c>
-      <c r="E20" s="4">
-        <f t="shared" si="1"/>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>37.25</v>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(OR($E20="NA",$B20="NA"),0,$E20/($D20^2))</f>
         <v>39.026629935720841</v>
       </c>
-      <c r="F20" s="4">
-        <f t="shared" si="2"/>
+      <c r="H20" s="4">
+        <f t="shared" si="3"/>
         <v>5.6965642558855336</v>
       </c>
-      <c r="G20" s="4">
-        <f t="shared" si="3"/>
+      <c r="I20" s="4">
+        <f t="shared" si="4"/>
         <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>37</v>
-      </c>
-      <c r="I20" t="s">
-        <v>71</v>
       </c>
       <c r="J20" t="s">
         <v>40</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>74</v>
+      </c>
+      <c r="L20" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20">
         <v>896</v>
       </c>
-      <c r="L20">
-        <f t="shared" si="4"/>
+      <c r="N20" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="6"/>
         <v>327040</v>
       </c>
-      <c r="N20" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" t="s">
-        <v>86</v>
-      </c>
-      <c r="P20" s="4" t="str" cm="1">
-        <f t="array" ref="P20">INDEX(_xlfn.TEXTSPLIT($Q20,{","," "}),1)</f>
+      <c r="Q20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" t="s">
+        <v>89</v>
+      </c>
+      <c r="S20" s="4" t="str" cm="1">
+        <f t="array" ref="S20">INDEX(_xlfn.TEXTSPLIT($T20,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q20" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="32.25">
+      <c r="T20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B21">
         <v>170</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>75</v>
       </c>
-      <c r="E21" s="4">
-        <f t="shared" si="1"/>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>165.25</v>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(OR($E21="NA",$B21="NA"),0,$E21/($D21^2))</f>
         <v>25.95155709342561</v>
       </c>
-      <c r="F21" s="4">
-        <f t="shared" si="2"/>
+      <c r="H21" s="4">
+        <f t="shared" si="3"/>
         <v>-7.3785085864096978</v>
       </c>
-      <c r="G21" s="4">
-        <f t="shared" si="3"/>
+      <c r="I21" s="4">
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="H21" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" t="s">
-        <v>90</v>
-      </c>
       <c r="J21" t="s">
-        <v>27</v>
-      </c>
-      <c r="K21">
+        <v>92</v>
+      </c>
+      <c r="K21" t="s">
+        <v>93</v>
+      </c>
+      <c r="L21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21">
         <v>82</v>
       </c>
-      <c r="L21">
-        <f t="shared" si="4"/>
+      <c r="N21" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="6"/>
         <v>29930</v>
       </c>
-      <c r="N21" t="s">
-        <v>33</v>
-      </c>
-      <c r="O21" t="s">
-        <v>22</v>
-      </c>
-      <c r="P21" s="4" t="str" cm="1">
-        <f t="array" ref="P21">INDEX(_xlfn.TEXTSPLIT($Q21,{","," "}),1)</f>
+      <c r="Q21" t="s">
+        <v>36</v>
+      </c>
+      <c r="R21" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21" s="4" t="str" cm="1">
+        <f t="array" ref="S21">INDEX(_xlfn.TEXTSPLIT($T21,{","," "}),1)</f>
         <v/>
       </c>
-      <c r="Q21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="32.25">
+      <c r="T21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="32.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B22">
         <v>183</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>78.2</v>
       </c>
-      <c r="E22" s="4">
-        <f t="shared" si="1"/>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>172.25</v>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(OR($E22="NA",$B22="NA"),0,$E22/($D22^2))</f>
         <v>23.350951058556539</v>
       </c>
-      <c r="F22" s="4">
-        <f t="shared" si="2"/>
+      <c r="H22" s="4">
+        <f t="shared" si="3"/>
         <v>-9.979114621278768</v>
       </c>
-      <c r="G22" s="4">
-        <f t="shared" si="3"/>
+      <c r="I22" s="4">
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
-      <c r="H22" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" t="s">
-        <v>19</v>
-      </c>
       <c r="J22" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22">
+        <v>55</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22">
         <v>31.5</v>
       </c>
-      <c r="L22">
-        <f t="shared" si="4"/>
+      <c r="N22" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="6"/>
         <v>11497.5</v>
       </c>
-      <c r="N22" t="s">
-        <v>93</v>
-      </c>
-      <c r="O22" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22" s="4" t="str" cm="1">
-        <f t="array" ref="P22">INDEX(_xlfn.TEXTSPLIT($Q22,{","," "}),1)</f>
+      <c r="Q22" t="s">
+        <v>96</v>
+      </c>
+      <c r="R22" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22" s="4" t="str" cm="1">
+        <f t="array" ref="S22">INDEX(_xlfn.TEXTSPLIT($T22,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="32.25">
+      <c r="T22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="32.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B23">
         <v>200</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
+        <v>78.5</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>140</v>
       </c>
-      <c r="E23" s="4">
-        <f t="shared" si="1"/>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>308.5</v>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(OR($E23="NA",$B23="NA"),0,$E23/($D23^2))</f>
         <v>35</v>
       </c>
-      <c r="F23" s="4">
-        <f t="shared" si="2"/>
+      <c r="H23" s="4">
+        <f t="shared" si="3"/>
         <v>1.6699343201646926</v>
       </c>
-      <c r="G23" s="4">
-        <f t="shared" si="3"/>
+      <c r="I23" s="4">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="H23" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" t="s">
-        <v>96</v>
-      </c>
       <c r="J23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23">
+        <v>39</v>
+      </c>
+      <c r="K23" t="s">
+        <v>99</v>
+      </c>
+      <c r="L23" t="s">
+        <v>35</v>
+      </c>
+      <c r="M23">
         <v>15</v>
       </c>
-      <c r="L23">
-        <f t="shared" si="4"/>
+      <c r="N23" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="6"/>
         <v>5475</v>
       </c>
-      <c r="N23" t="s">
-        <v>25</v>
-      </c>
-      <c r="O23" t="s">
-        <v>28</v>
-      </c>
-      <c r="P23" s="4" t="str" cm="1">
-        <f t="array" ref="P23">INDEX(_xlfn.TEXTSPLIT($Q23,{","," "}),1)</f>
+      <c r="Q23" t="s">
+        <v>28</v>
+      </c>
+      <c r="R23" t="s">
+        <v>31</v>
+      </c>
+      <c r="S23" s="4" t="str" cm="1">
+        <f t="array" ref="S23">INDEX(_xlfn.TEXTSPLIT($T23,{","," "}),1)</f>
         <v>The Empire Strikes Back</v>
       </c>
-      <c r="Q23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="32.25">
+      <c r="T23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="32.25">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B24">
         <v>190</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
+        <v>74.5</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>113</v>
       </c>
-      <c r="E24" s="4">
-        <f t="shared" si="1"/>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>249</v>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(OR($E24="NA",$B24="NA"),0,$E24/($D24^2))</f>
         <v>31.301939058171747</v>
       </c>
-      <c r="F24" s="4">
-        <f t="shared" si="2"/>
+      <c r="H24" s="4">
+        <f t="shared" si="3"/>
         <v>-2.0281266216635601</v>
       </c>
-      <c r="G24" s="4">
-        <f t="shared" si="3"/>
+      <c r="I24" s="4">
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="H24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" t="s">
-        <v>71</v>
-      </c>
       <c r="J24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24">
+        <v>39</v>
+      </c>
+      <c r="K24" t="s">
+        <v>74</v>
+      </c>
+      <c r="L24" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24">
         <v>53</v>
       </c>
-      <c r="L24">
-        <f t="shared" si="4"/>
+      <c r="N24" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="6"/>
         <v>19345</v>
       </c>
-      <c r="N24" t="s">
-        <v>99</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="Q24" t="s">
+        <v>102</v>
+      </c>
+      <c r="R24" t="s">
+        <v>103</v>
+      </c>
+      <c r="S24" s="4" t="str" cm="1">
+        <f t="array" ref="S24">INDEX(_xlfn.TEXTSPLIT($T24,{","," "}),1)</f>
+        <v>The Empire Strikes Back</v>
+      </c>
+      <c r="T24" t="s">
         <v>100</v>
       </c>
-      <c r="P24" s="4" t="str" cm="1">
-        <f t="array" ref="P24">INDEX(_xlfn.TEXTSPLIT($Q24,{","," "}),1)</f>
-        <v>The Empire Strikes Back</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="32.25">
+    </row>
+    <row r="25" spans="1:20" ht="32.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B25">
         <v>177</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
+        <v>69.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
         <v>1.77</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>79</v>
       </c>
-      <c r="E25" s="4">
-        <f t="shared" si="1"/>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="G25" s="4">
+        <f>IF(OR($E25="NA",$B25="NA"),0,$E25/($D25^2))</f>
         <v>25.216253311628201</v>
       </c>
-      <c r="F25" s="4">
-        <f t="shared" si="2"/>
+      <c r="H25" s="4">
+        <f t="shared" si="3"/>
         <v>-8.1138123682071068</v>
       </c>
-      <c r="G25" s="4">
-        <f t="shared" si="3"/>
+      <c r="I25" s="4">
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
-      <c r="H25" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" t="s">
-        <v>102</v>
-      </c>
       <c r="J25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25">
+        <v>55</v>
+      </c>
+      <c r="K25" t="s">
+        <v>105</v>
+      </c>
+      <c r="L25" t="s">
+        <v>43</v>
+      </c>
+      <c r="M25">
         <v>31</v>
       </c>
-      <c r="L25">
-        <f t="shared" si="4"/>
+      <c r="N25" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="6"/>
         <v>11315</v>
       </c>
-      <c r="N25" t="s">
-        <v>103</v>
-      </c>
-      <c r="O25" t="s">
-        <v>22</v>
-      </c>
-      <c r="P25" s="4" t="str" cm="1">
-        <f t="array" ref="P25">INDEX(_xlfn.TEXTSPLIT($Q25,{","," "}),1)</f>
+      <c r="Q25" t="s">
+        <v>106</v>
+      </c>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25" s="4" t="str" cm="1">
+        <f t="array" ref="S25">INDEX(_xlfn.TEXTSPLIT($T25,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="32.25">
+      <c r="T25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="32.25">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B26">
         <v>175</v>
       </c>
       <c r="C26">
         <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>79</v>
       </c>
-      <c r="E26" s="4">
-        <f t="shared" si="1"/>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(OR($E26="NA",$B26="NA"),0,$E26/($D26^2))</f>
         <v>25.795918367346939</v>
       </c>
-      <c r="F26" s="4">
-        <f t="shared" si="2"/>
+      <c r="H26" s="4">
+        <f t="shared" si="3"/>
         <v>-7.5341473124883684</v>
       </c>
-      <c r="G26" s="4">
-        <f t="shared" si="3"/>
+      <c r="I26" s="4">
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
-      <c r="H26" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" t="s">
-        <v>41</v>
-      </c>
       <c r="J26" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26">
+        <v>39</v>
+      </c>
+      <c r="K26" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26">
         <v>37</v>
       </c>
-      <c r="L26">
-        <f t="shared" si="4"/>
+      <c r="N26" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="6"/>
         <v>13505</v>
       </c>
-      <c r="N26" t="s">
-        <v>106</v>
-      </c>
-      <c r="O26" t="s">
-        <v>22</v>
-      </c>
-      <c r="P26" s="4" t="str" cm="1">
-        <f t="array" ref="P26">INDEX(_xlfn.TEXTSPLIT($Q26,{","," "}),1)</f>
+      <c r="Q26" t="s">
+        <v>109</v>
+      </c>
+      <c r="R26" t="s">
+        <v>25</v>
+      </c>
+      <c r="S26" s="4" t="str" cm="1">
+        <f t="array" ref="S26">INDEX(_xlfn.TEXTSPLIT($T26,{","," "}),1)</f>
         <v>The Empire Strikes Back</v>
       </c>
-      <c r="Q26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="32.25">
+      <c r="T26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="32.25">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B27">
         <v>180</v>
       </c>
       <c r="C27">
         <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>83</v>
       </c>
-      <c r="E27" s="4">
-        <f t="shared" si="1"/>
+      <c r="F27">
+        <f t="shared" si="2"/>
+        <v>182.75</v>
+      </c>
+      <c r="G27" s="4">
+        <f>IF(OR($E27="NA",$B27="NA"),0,$E27/($D27^2))</f>
         <v>25.617283950617281</v>
       </c>
-      <c r="F27" s="4">
-        <f t="shared" si="2"/>
+      <c r="H27" s="4">
+        <f t="shared" si="3"/>
         <v>-7.7127817292180261</v>
       </c>
-      <c r="G27" s="4">
-        <f t="shared" si="3"/>
+      <c r="I27" s="4">
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="H27" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" t="s">
-        <v>108</v>
-      </c>
       <c r="J27" t="s">
-        <v>76</v>
-      </c>
-      <c r="K27">
+        <v>39</v>
+      </c>
+      <c r="K27" t="s">
+        <v>111</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27">
         <v>41</v>
       </c>
-      <c r="L27">
-        <f t="shared" si="4"/>
+      <c r="N27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="6"/>
         <v>14965</v>
       </c>
-      <c r="N27" t="s">
-        <v>109</v>
-      </c>
-      <c r="O27" t="s">
-        <v>110</v>
-      </c>
-      <c r="P27" s="4" t="str" cm="1">
-        <f t="array" ref="P27">INDEX(_xlfn.TEXTSPLIT($Q27,{","," "}),1)</f>
+      <c r="Q27" t="s">
+        <v>112</v>
+      </c>
+      <c r="R27" t="s">
+        <v>113</v>
+      </c>
+      <c r="S27" s="4" t="str" cm="1">
+        <f t="array" ref="S27">INDEX(_xlfn.TEXTSPLIT($T27,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="32.25">
+      <c r="T27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="32.25">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B28">
         <v>150</v>
       </c>
       <c r="C28">
         <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G28" s="4">
+        <f>IF(OR($E28="NA",$B28="NA"),0,$E28/($D28^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J28" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28">
+        <v>48</v>
+      </c>
+      <c r="N28" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="6"/>
+        <v>17520</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>117</v>
+      </c>
+      <c r="R28" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G28" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H28" t="s">
-        <v>113</v>
-      </c>
-      <c r="I28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28">
-        <v>48</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="4"/>
-        <v>17520</v>
-      </c>
-      <c r="N28" t="s">
-        <v>114</v>
-      </c>
-      <c r="O28" t="s">
-        <v>22</v>
-      </c>
-      <c r="P28" s="4" t="str" cm="1">
-        <f t="array" ref="P28">INDEX(_xlfn.TEXTSPLIT($Q28,{","," "}),1)</f>
+      <c r="S28" s="4" t="str" cm="1">
+        <f t="array" ref="S28">INDEX(_xlfn.TEXTSPLIT($T28,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="32.25">
+      <c r="T28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="32.25">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C29" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G29" s="4">
+        <f>IF(OR($E29="NA",$B29="NA"),0,$E29/($D29^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J29" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O29" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>28</v>
+      </c>
+      <c r="R29" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G29" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H29" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s">
-        <v>40</v>
-      </c>
-      <c r="K29" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>22</v>
-      </c>
-      <c r="P29" s="4" t="str" cm="1">
-        <f t="array" ref="P29">INDEX(_xlfn.TEXTSPLIT($Q29,{","," "}),1)</f>
+      <c r="S29" s="4" t="str" cm="1">
+        <f t="array" ref="S29">INDEX(_xlfn.TEXTSPLIT($T29,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="32.25">
+      <c r="T29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="32.25">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B30">
         <v>88</v>
       </c>
       <c r="C30">
         <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>20</v>
       </c>
-      <c r="E30" s="4">
-        <f t="shared" si="1"/>
+      <c r="F30">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="G30" s="4">
+        <f>IF(OR($E30="NA",$B30="NA"),0,$E30/($D30^2))</f>
         <v>25.826446280991735</v>
       </c>
-      <c r="F30" s="4">
-        <f t="shared" si="2"/>
+      <c r="H30" s="4">
+        <f t="shared" si="3"/>
         <v>-7.503619398843572</v>
       </c>
-      <c r="G30" s="4">
-        <f t="shared" si="3"/>
+      <c r="I30" s="4">
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="H30" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30" t="s">
-        <v>40</v>
-      </c>
       <c r="J30" t="s">
-        <v>40</v>
-      </c>
-      <c r="K30">
+        <v>43</v>
+      </c>
+      <c r="K30" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" t="s">
+        <v>43</v>
+      </c>
+      <c r="M30">
         <v>8</v>
       </c>
-      <c r="L30">
-        <f t="shared" si="4"/>
+      <c r="N30" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="6"/>
         <v>2920</v>
       </c>
-      <c r="N30" t="s">
+      <c r="Q30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R30" t="s">
+        <v>122</v>
+      </c>
+      <c r="S30" s="4" t="str" cm="1">
+        <f t="array" ref="S30">INDEX(_xlfn.TEXTSPLIT($T30,{","," "}),1)</f>
+        <v>Return of the Jedi</v>
+      </c>
+      <c r="T30" t="s">
         <v>118</v>
       </c>
-      <c r="O30" t="s">
-        <v>119</v>
-      </c>
-      <c r="P30" s="4" t="str" cm="1">
-        <f t="array" ref="P30">INDEX(_xlfn.TEXTSPLIT($Q30,{","," "}),1)</f>
-        <v>Return of the Jedi</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="32.25">
+    </row>
+    <row r="31" spans="1:20" ht="32.25">
       <c r="A31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B31">
         <v>160</v>
       </c>
       <c r="C31">
         <f t="shared" si="0"/>
+        <v>62.5</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>68</v>
       </c>
-      <c r="E31" s="4">
-        <f t="shared" si="1"/>
+      <c r="F31">
+        <f t="shared" si="2"/>
+        <v>149.75</v>
+      </c>
+      <c r="G31" s="4">
+        <f>IF(OR($E31="NA",$B31="NA"),0,$E31/($D31^2))</f>
         <v>26.562499999999996</v>
       </c>
-      <c r="F31" s="4">
-        <f t="shared" si="2"/>
+      <c r="H31" s="4">
+        <f t="shared" si="3"/>
         <v>-6.767565679835311</v>
       </c>
-      <c r="G31" s="4">
-        <f t="shared" si="3"/>
+      <c r="I31" s="4">
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="H31" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" t="s">
-        <v>89</v>
-      </c>
       <c r="J31" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K31" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N31" t="s">
-        <v>121</v>
-      </c>
-      <c r="O31" t="s">
-        <v>122</v>
-      </c>
-      <c r="P31" s="4" t="str" cm="1">
-        <f t="array" ref="P31">INDEX(_xlfn.TEXTSPLIT($Q31,{","," "}),1)</f>
+        <v>92</v>
+      </c>
+      <c r="L31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O31" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>124</v>
+      </c>
+      <c r="R31" t="s">
+        <v>125</v>
+      </c>
+      <c r="S31" s="4" t="str" cm="1">
+        <f t="array" ref="S31">INDEX(_xlfn.TEXTSPLIT($T31,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q31" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="32.25">
+      <c r="T31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="32.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B32">
         <v>193</v>
       </c>
       <c r="C32">
         <f t="shared" si="0"/>
+        <v>75.5</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
         <v>1.93</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>89</v>
       </c>
-      <c r="E32" s="4">
-        <f t="shared" si="1"/>
+      <c r="F32">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+      <c r="G32" s="4">
+        <f>IF(OR($E32="NA",$B32="NA"),0,$E32/($D32^2))</f>
         <v>23.893258879433006</v>
       </c>
-      <c r="F32" s="4">
-        <f t="shared" si="2"/>
+      <c r="H32" s="4">
+        <f t="shared" si="3"/>
         <v>-9.4368068004023016</v>
       </c>
-      <c r="G32" s="4">
-        <f t="shared" si="3"/>
+      <c r="I32" s="4">
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
-      <c r="H32" t="s">
-        <v>40</v>
-      </c>
-      <c r="I32" t="s">
-        <v>19</v>
-      </c>
       <c r="J32" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32">
+        <v>43</v>
+      </c>
+      <c r="K32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L32" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32">
         <v>92</v>
       </c>
-      <c r="L32">
-        <f t="shared" si="4"/>
+      <c r="N32" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="6"/>
         <v>33580</v>
       </c>
-      <c r="N32" t="s">
+      <c r="Q32" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" t="s">
         <v>25</v>
       </c>
-      <c r="O32" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="4" t="str" cm="1">
-        <f t="array" ref="P32">INDEX(_xlfn.TEXTSPLIT($Q32,{","," "}),1)</f>
+      <c r="S32" s="4" t="str" cm="1">
+        <f t="array" ref="S32">INDEX(_xlfn.TEXTSPLIT($T32,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="32.25">
+      <c r="T32" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="32.25">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B33">
         <v>191</v>
       </c>
       <c r="C33">
         <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="1"/>
         <v>1.91</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>90</v>
       </c>
-      <c r="E33" s="4">
-        <f t="shared" si="1"/>
+      <c r="F33">
+        <f t="shared" si="2"/>
+        <v>198.25</v>
+      </c>
+      <c r="G33" s="4">
+        <f>IF(OR($E33="NA",$B33="NA"),0,$E33/($D33^2))</f>
         <v>24.670376360297141</v>
       </c>
-      <c r="F33" s="4">
-        <f t="shared" si="2"/>
+      <c r="H33" s="4">
+        <f t="shared" si="3"/>
         <v>-8.6596893195381668</v>
       </c>
-      <c r="G33" s="4">
-        <f t="shared" si="3"/>
+      <c r="I33" s="4">
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="H33" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" t="s">
-        <v>126</v>
-      </c>
       <c r="J33" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N33" t="s">
-        <v>127</v>
-      </c>
-      <c r="O33" t="s">
-        <v>128</v>
-      </c>
-      <c r="P33" s="4" t="str" cm="1">
-        <f t="array" ref="P33">INDEX(_xlfn.TEXTSPLIT($Q33,{","," "}),1)</f>
+        <v>129</v>
+      </c>
+      <c r="L33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M33" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O33" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>130</v>
+      </c>
+      <c r="R33" t="s">
+        <v>131</v>
+      </c>
+      <c r="S33" s="4" t="str" cm="1">
+        <f t="array" ref="S33">INDEX(_xlfn.TEXTSPLIT($T33,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q33" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="32.25">
+      <c r="T33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="32.25">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B34">
         <v>170</v>
       </c>
       <c r="C34">
         <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G34" s="4">
+        <f>IF(OR($E34="NA",$B34="NA"),0,$E34/($D34^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J34" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34">
+        <v>91</v>
+      </c>
+      <c r="N34" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="6"/>
+        <v>33215</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>133</v>
+      </c>
+      <c r="R34" t="s">
         <v>25</v>
       </c>
-      <c r="E34" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G34" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H34" t="s">
-        <v>18</v>
-      </c>
-      <c r="I34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34">
-        <v>91</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="4"/>
-        <v>33215</v>
-      </c>
-      <c r="N34" t="s">
-        <v>130</v>
-      </c>
-      <c r="O34" t="s">
-        <v>22</v>
-      </c>
-      <c r="P34" s="4" t="str" cm="1">
-        <f t="array" ref="P34">INDEX(_xlfn.TEXTSPLIT($Q34,{","," "}),1)</f>
+      <c r="S34" s="4" t="str" cm="1">
+        <f t="array" ref="S34">INDEX(_xlfn.TEXTSPLIT($T34,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q34" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="32.25">
+      <c r="T34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="32.25">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B35">
         <v>196</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="1"/>
         <v>1.96</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>66</v>
       </c>
-      <c r="E35" s="4">
-        <f t="shared" si="1"/>
+      <c r="F35">
+        <f t="shared" si="2"/>
+        <v>145.5</v>
+      </c>
+      <c r="G35" s="4">
+        <f>IF(OR($E35="NA",$B35="NA"),0,$E35/($D35^2))</f>
         <v>17.180341524364849</v>
       </c>
-      <c r="F35" s="4">
-        <f t="shared" si="2"/>
+      <c r="H35" s="4">
+        <f t="shared" si="3"/>
         <v>-16.149724155470459</v>
       </c>
-      <c r="G35" s="4">
-        <f t="shared" si="3"/>
+      <c r="I35" s="4">
+        <f t="shared" si="4"/>
         <v>53</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
+        <v>39</v>
+      </c>
+      <c r="K35" t="s">
+        <v>79</v>
+      </c>
+      <c r="L35" t="s">
+        <v>79</v>
+      </c>
+      <c r="M35">
+        <v>52</v>
+      </c>
+      <c r="N35" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="6"/>
+        <v>18980</v>
+      </c>
+      <c r="Q35" t="s">
         <v>36</v>
       </c>
-      <c r="I35" t="s">
-        <v>76</v>
-      </c>
-      <c r="J35" t="s">
-        <v>76</v>
-      </c>
-      <c r="K35">
-        <v>52</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="4"/>
-        <v>18980</v>
-      </c>
-      <c r="N35" t="s">
-        <v>33</v>
-      </c>
-      <c r="O35" t="s">
-        <v>132</v>
-      </c>
-      <c r="P35" s="4" t="str" cm="1">
-        <f t="array" ref="P35">INDEX(_xlfn.TEXTSPLIT($Q35,{","," "}),1)</f>
+      <c r="R35" t="s">
+        <v>135</v>
+      </c>
+      <c r="S35" s="4" t="str" cm="1">
+        <f t="array" ref="S35">INDEX(_xlfn.TEXTSPLIT($T35,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="32.25">
+      <c r="T35" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="32.25">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B36">
         <v>224</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
         <v>2.2400000000000002</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>82</v>
       </c>
-      <c r="E36" s="4">
-        <f t="shared" si="1"/>
+      <c r="F36">
+        <f t="shared" si="2"/>
+        <v>180.75</v>
+      </c>
+      <c r="G36" s="4">
+        <f>IF(OR($E36="NA",$B36="NA"),0,$E36/($D36^2))</f>
         <v>16.342474489795915</v>
       </c>
-      <c r="F36" s="4">
-        <f t="shared" si="2"/>
+      <c r="H36" s="4">
+        <f t="shared" si="3"/>
         <v>-16.987591190039392</v>
       </c>
-      <c r="G36" s="4">
-        <f t="shared" si="3"/>
+      <c r="I36" s="4">
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" t="s">
+        <v>39</v>
+      </c>
+      <c r="K36" t="s">
+        <v>92</v>
+      </c>
+      <c r="L36" t="s">
+        <v>79</v>
+      </c>
+      <c r="M36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O36" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q36" t="s">
         <v>36</v>
       </c>
-      <c r="I36" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" t="s">
-        <v>76</v>
-      </c>
-      <c r="K36" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N36" t="s">
-        <v>33</v>
-      </c>
-      <c r="O36" t="s">
-        <v>132</v>
-      </c>
-      <c r="P36" s="4" t="str" cm="1">
-        <f t="array" ref="P36">INDEX(_xlfn.TEXTSPLIT($Q36,{","," "}),1)</f>
+      <c r="R36" t="s">
+        <v>135</v>
+      </c>
+      <c r="S36" s="4" t="str" cm="1">
+        <f t="array" ref="S36">INDEX(_xlfn.TEXTSPLIT($T36,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q36" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="32.25">
+      <c r="T36" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="32.25">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B37">
         <v>206</v>
       </c>
       <c r="C37">
         <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="1"/>
         <v>2.06</v>
       </c>
-      <c r="D37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="4">
-        <f t="shared" si="1"/>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G37" s="4">
+        <f>IF(OR($E37="NA",$B37="NA"),0,$E37/($D37^2))</f>
         <v>0</v>
       </c>
-      <c r="F37" s="4">
-        <f t="shared" si="2"/>
+      <c r="H37" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G37" s="4">
-        <f t="shared" si="3"/>
+      <c r="I37" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
+        <v>39</v>
+      </c>
+      <c r="K37" t="s">
+        <v>74</v>
+      </c>
+      <c r="L37" t="s">
+        <v>79</v>
+      </c>
+      <c r="M37" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O37" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q37" t="s">
         <v>36</v>
       </c>
-      <c r="I37" t="s">
-        <v>71</v>
-      </c>
-      <c r="J37" t="s">
-        <v>76</v>
-      </c>
-      <c r="K37" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N37" t="s">
-        <v>33</v>
-      </c>
-      <c r="O37" t="s">
-        <v>132</v>
-      </c>
-      <c r="P37" s="4" t="str" cm="1">
-        <f t="array" ref="P37">INDEX(_xlfn.TEXTSPLIT($Q37,{","," "}),1)</f>
+      <c r="R37" t="s">
+        <v>135</v>
+      </c>
+      <c r="S37" s="4" t="str" cm="1">
+        <f t="array" ref="S37">INDEX(_xlfn.TEXTSPLIT($T37,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="32.25">
+      <c r="T37" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="32.25">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B38">
         <v>183</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="4">
-        <f t="shared" si="1"/>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G38" s="4">
+        <f>IF(OR($E38="NA",$B38="NA"),0,$E38/($D38^2))</f>
         <v>0</v>
       </c>
-      <c r="F38" s="4">
-        <f t="shared" si="2"/>
+      <c r="H38" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G38" s="4">
-        <f t="shared" si="3"/>
+      <c r="I38" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H38" t="s">
-        <v>40</v>
-      </c>
-      <c r="I38" t="s">
-        <v>19</v>
-      </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N38" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" t="s">
-        <v>25</v>
-      </c>
-      <c r="P38" s="4" t="str" cm="1">
-        <f t="array" ref="P38">INDEX(_xlfn.TEXTSPLIT($Q38,{","," "}),1)</f>
+        <v>22</v>
+      </c>
+      <c r="L38" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O38" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>36</v>
+      </c>
+      <c r="R38" t="s">
+        <v>28</v>
+      </c>
+      <c r="S38" s="4" t="str" cm="1">
+        <f t="array" ref="S38">INDEX(_xlfn.TEXTSPLIT($T38,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="32.25">
+      <c r="T38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B39">
         <v>137</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
+        <v>53.5</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="1"/>
         <v>1.37</v>
       </c>
-      <c r="D39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="4">
-        <f t="shared" si="1"/>
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G39" s="4">
+        <f>IF(OR($E39="NA",$B39="NA"),0,$E39/($D39^2))</f>
         <v>0</v>
       </c>
-      <c r="F39" s="4">
-        <f t="shared" si="2"/>
+      <c r="H39" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G39" s="4">
-        <f t="shared" si="3"/>
+      <c r="I39" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H39" t="s">
-        <v>52</v>
-      </c>
-      <c r="I39" t="s">
-        <v>138</v>
-      </c>
       <c r="J39" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N39" t="s">
-        <v>139</v>
-      </c>
-      <c r="O39" t="s">
-        <v>140</v>
-      </c>
-      <c r="P39" s="4" t="str" cm="1">
-        <f t="array" ref="P39">INDEX(_xlfn.TEXTSPLIT($Q39,{","," "}),1)</f>
+        <v>141</v>
+      </c>
+      <c r="L39" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O39" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>142</v>
+      </c>
+      <c r="R39" t="s">
+        <v>143</v>
+      </c>
+      <c r="S39" s="4" t="str" cm="1">
+        <f t="array" ref="S39">INDEX(_xlfn.TEXTSPLIT($T39,{","," "}),1)</f>
         <v/>
       </c>
-      <c r="Q39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="32.25">
+      <c r="T39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="32.25">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B40">
         <v>112</v>
       </c>
       <c r="C40">
         <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="1"/>
         <v>1.1200000000000001</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>40</v>
       </c>
-      <c r="E40" s="4">
-        <f t="shared" si="1"/>
+      <c r="F40">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="G40" s="4">
+        <f>IF(OR($E40="NA",$B40="NA"),0,$E40/($D40^2))</f>
         <v>31.887755102040813</v>
       </c>
-      <c r="F40" s="4">
-        <f t="shared" si="2"/>
+      <c r="H40" s="4">
+        <f t="shared" si="3"/>
         <v>-1.442310577794494</v>
       </c>
-      <c r="G40" s="4">
-        <f t="shared" si="3"/>
+      <c r="I40" s="4">
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="H40" t="s">
-        <v>36</v>
-      </c>
-      <c r="I40" t="s">
-        <v>143</v>
-      </c>
       <c r="J40" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="K40" t="s">
-        <v>25</v>
-      </c>
-      <c r="L40" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N40" t="s">
-        <v>144</v>
-      </c>
-      <c r="O40" t="s">
-        <v>145</v>
-      </c>
-      <c r="P40" s="4" t="str" cm="1">
-        <f t="array" ref="P40">INDEX(_xlfn.TEXTSPLIT($Q40,{","," "}),1)</f>
+        <v>146</v>
+      </c>
+      <c r="L40" t="s">
+        <v>79</v>
+      </c>
+      <c r="M40" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O40" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>147</v>
+      </c>
+      <c r="R40" t="s">
+        <v>148</v>
+      </c>
+      <c r="S40" s="4" t="str" cm="1">
+        <f t="array" ref="S40">INDEX(_xlfn.TEXTSPLIT($T40,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q40" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="32.25">
+      <c r="T40" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="32.25">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B41">
         <v>183</v>
       </c>
       <c r="C41">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="4">
-        <f t="shared" si="1"/>
+      <c r="E41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G41" s="4">
+        <f>IF(OR($E41="NA",$B41="NA"),0,$E41/($D41^2))</f>
         <v>0</v>
       </c>
-      <c r="F41" s="4">
-        <f t="shared" si="2"/>
+      <c r="H41" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G41" s="4">
-        <f t="shared" si="3"/>
+      <c r="I41" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H41" t="s">
-        <v>52</v>
-      </c>
-      <c r="I41" t="s">
-        <v>102</v>
-      </c>
       <c r="J41" t="s">
-        <v>40</v>
-      </c>
-      <c r="K41">
+        <v>55</v>
+      </c>
+      <c r="K41" t="s">
+        <v>105</v>
+      </c>
+      <c r="L41" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41">
         <v>62</v>
       </c>
-      <c r="L41">
-        <f t="shared" si="4"/>
+      <c r="N41" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="6"/>
         <v>22630</v>
       </c>
-      <c r="N41" t="s">
-        <v>33</v>
-      </c>
-      <c r="O41" t="s">
-        <v>25</v>
-      </c>
-      <c r="P41" s="4" t="str" cm="1">
-        <f t="array" ref="P41">INDEX(_xlfn.TEXTSPLIT($Q41,{","," "}),1)</f>
+      <c r="Q41" t="s">
+        <v>36</v>
+      </c>
+      <c r="R41" t="s">
+        <v>28</v>
+      </c>
+      <c r="S41" s="4" t="str" cm="1">
+        <f t="array" ref="S41">INDEX(_xlfn.TEXTSPLIT($T41,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="32.25">
+      <c r="T41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B42">
         <v>163</v>
       </c>
       <c r="C42">
         <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="1"/>
         <v>1.63</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G42" s="4">
+        <f>IF(OR($E42="NA",$B42="NA"),0,$E42/($D42^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J42" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42">
+        <v>72</v>
+      </c>
+      <c r="N42" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="6"/>
+        <v>26280</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>24</v>
+      </c>
+      <c r="R42" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F42" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G42" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H42" t="s">
-        <v>52</v>
-      </c>
-      <c r="I42" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" t="s">
-        <v>40</v>
-      </c>
-      <c r="K42">
-        <v>72</v>
-      </c>
-      <c r="L42">
-        <f t="shared" si="4"/>
-        <v>26280</v>
-      </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" t="s">
-        <v>22</v>
-      </c>
-      <c r="P42" s="4" t="str" cm="1">
-        <f t="array" ref="P42">INDEX(_xlfn.TEXTSPLIT($Q42,{","," "}),1)</f>
+      <c r="S42" s="4" t="str" cm="1">
+        <f t="array" ref="S42">INDEX(_xlfn.TEXTSPLIT($T42,{","," "}),1)</f>
         <v/>
       </c>
-      <c r="Q42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="32.25">
+      <c r="T42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="32.25">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B43">
         <v>175</v>
       </c>
       <c r="C43">
         <f t="shared" si="0"/>
+        <v>68.5</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>80</v>
       </c>
-      <c r="E43" s="4">
-        <f t="shared" si="1"/>
+      <c r="F43">
+        <f t="shared" si="2"/>
+        <v>176.25</v>
+      </c>
+      <c r="G43" s="4">
+        <f>IF(OR($E43="NA",$B43="NA"),0,$E43/($D43^2))</f>
         <v>26.122448979591837</v>
       </c>
-      <c r="F43" s="4">
-        <f t="shared" si="2"/>
+      <c r="H43" s="4">
+        <f t="shared" si="3"/>
         <v>-7.2076167002434701</v>
       </c>
-      <c r="G43" s="4">
-        <f t="shared" si="3"/>
+      <c r="I43" s="4">
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="H43" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" t="s">
-        <v>32</v>
-      </c>
       <c r="J43" t="s">
-        <v>27</v>
-      </c>
-      <c r="K43">
+        <v>39</v>
+      </c>
+      <c r="K43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L43" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43">
         <v>54</v>
       </c>
-      <c r="L43">
-        <f t="shared" si="4"/>
+      <c r="N43" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="6"/>
         <v>19710</v>
       </c>
-      <c r="N43" t="s">
-        <v>149</v>
-      </c>
-      <c r="O43" t="s">
-        <v>150</v>
-      </c>
-      <c r="P43" s="4" t="str" cm="1">
-        <f t="array" ref="P43">INDEX(_xlfn.TEXTSPLIT($Q43,{","," "}),1)</f>
+      <c r="Q43" t="s">
+        <v>152</v>
+      </c>
+      <c r="R43" t="s">
+        <v>153</v>
+      </c>
+      <c r="S43" s="4" t="str" cm="1">
+        <f t="array" ref="S43">INDEX(_xlfn.TEXTSPLIT($T43,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q43" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="32.25">
+      <c r="T43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="32.25">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B44">
         <v>180</v>
       </c>
       <c r="C44">
         <f t="shared" si="0"/>
+        <v>70.5</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
-      <c r="D44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="4">
-        <f t="shared" si="1"/>
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G44" s="4">
+        <f>IF(OR($E44="NA",$B44="NA"),0,$E44/($D44^2))</f>
         <v>0</v>
       </c>
-      <c r="F44" s="4">
-        <f t="shared" si="2"/>
+      <c r="H44" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G44" s="4">
-        <f t="shared" si="3"/>
+      <c r="I44" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H44" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" t="s">
-        <v>90</v>
-      </c>
       <c r="J44" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="K44" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N44" t="s">
-        <v>153</v>
-      </c>
-      <c r="O44" t="s">
-        <v>154</v>
-      </c>
-      <c r="P44" s="4" t="str" cm="1">
-        <f t="array" ref="P44">INDEX(_xlfn.TEXTSPLIT($Q44,{","," "}),1)</f>
+        <v>93</v>
+      </c>
+      <c r="L44" t="s">
+        <v>155</v>
+      </c>
+      <c r="M44" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O44" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>156</v>
+      </c>
+      <c r="R44" t="s">
+        <v>157</v>
+      </c>
+      <c r="S44" s="4" t="str" cm="1">
+        <f t="array" ref="S44">INDEX(_xlfn.TEXTSPLIT($T44,{","," "}),1)</f>
         <v>Return of the Jedi</v>
       </c>
-      <c r="Q44" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="32.25">
+      <c r="T44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B45">
         <v>178</v>
       </c>
       <c r="C45">
         <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="1"/>
         <v>1.78</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>55</v>
       </c>
-      <c r="E45" s="4">
-        <f t="shared" si="1"/>
+      <c r="F45">
+        <f t="shared" si="2"/>
+        <v>121.25</v>
+      </c>
+      <c r="G45" s="4">
+        <f>IF(OR($E45="NA",$B45="NA"),0,$E45/($D45^2))</f>
         <v>17.35891932836763</v>
       </c>
-      <c r="F45" s="4">
-        <f t="shared" si="2"/>
+      <c r="H45" s="4">
+        <f t="shared" si="3"/>
         <v>-15.971146351467677</v>
       </c>
-      <c r="G45" s="4">
-        <f t="shared" si="3"/>
+      <c r="I45" s="4">
+        <f t="shared" si="4"/>
         <v>52</v>
       </c>
-      <c r="H45" t="s">
-        <v>36</v>
-      </c>
-      <c r="I45" t="s">
-        <v>20</v>
-      </c>
       <c r="J45" t="s">
-        <v>81</v>
-      </c>
-      <c r="K45">
+        <v>39</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>84</v>
+      </c>
+      <c r="M45">
         <v>48</v>
       </c>
-      <c r="L45">
-        <f t="shared" si="4"/>
+      <c r="N45" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="6"/>
         <v>17520</v>
-      </c>
-      <c r="N45" t="s">
-        <v>153</v>
-      </c>
-      <c r="O45" t="s">
-        <v>154</v>
-      </c>
-      <c r="P45" s="4" t="str" cm="1">
-        <f t="array" ref="P45">INDEX(_xlfn.TEXTSPLIT($Q45,{","," "}),1)</f>
-        <v/>
       </c>
       <c r="Q45" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" ht="32.25">
+      <c r="R45" t="s">
+        <v>157</v>
+      </c>
+      <c r="S45" s="4" t="str" cm="1">
+        <f t="array" ref="S45">INDEX(_xlfn.TEXTSPLIT($T45,{","," "}),1)</f>
+        <v/>
+      </c>
+      <c r="T45" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="32.25">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B46">
         <v>94</v>
       </c>
       <c r="C46">
         <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="1"/>
         <v>0.94</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>45</v>
       </c>
-      <c r="E46" s="4">
-        <f t="shared" si="1"/>
+      <c r="F46">
+        <f t="shared" si="2"/>
+        <v>99</v>
+      </c>
+      <c r="G46" s="4">
+        <f>IF(OR($E46="NA",$B46="NA"),0,$E46/($D46^2))</f>
         <v>50.928021729289277</v>
       </c>
-      <c r="F46" s="4">
-        <f t="shared" si="2"/>
+      <c r="H46" s="4">
+        <f t="shared" si="3"/>
         <v>17.59795604945397</v>
       </c>
-      <c r="G46" s="4">
-        <f t="shared" si="3"/>
+      <c r="I46" s="4">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="H46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" t="s">
-        <v>138</v>
-      </c>
       <c r="J46" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K46" t="s">
-        <v>25</v>
-      </c>
-      <c r="L46" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N46" t="s">
-        <v>158</v>
-      </c>
-      <c r="O46" t="s">
-        <v>159</v>
-      </c>
-      <c r="P46" s="4" t="str" cm="1">
-        <f t="array" ref="P46">INDEX(_xlfn.TEXTSPLIT($Q46,{","," "}),1)</f>
+        <v>141</v>
+      </c>
+      <c r="L46" t="s">
+        <v>30</v>
+      </c>
+      <c r="M46" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O46" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>161</v>
+      </c>
+      <c r="R46" t="s">
+        <v>162</v>
+      </c>
+      <c r="S46" s="4" t="str" cm="1">
+        <f t="array" ref="S46">INDEX(_xlfn.TEXTSPLIT($T46,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="32.25">
+      <c r="T46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="32.25">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B47">
         <v>122</v>
       </c>
       <c r="C47">
         <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="1"/>
         <v>1.22</v>
       </c>
-      <c r="D47" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="4">
-        <f t="shared" si="1"/>
+      <c r="E47" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G47" s="4">
+        <f>IF(OR($E47="NA",$B47="NA"),0,$E47/($D47^2))</f>
         <v>0</v>
       </c>
-      <c r="F47" s="4">
-        <f t="shared" si="2"/>
+      <c r="H47" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G47" s="4">
-        <f t="shared" si="3"/>
+      <c r="I47" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H47" t="s">
-        <v>36</v>
-      </c>
-      <c r="I47" t="s">
-        <v>31</v>
-      </c>
       <c r="J47" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K47" t="s">
-        <v>25</v>
-      </c>
-      <c r="L47" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N47" t="s">
-        <v>161</v>
-      </c>
-      <c r="O47" t="s">
-        <v>162</v>
-      </c>
-      <c r="P47" s="4" t="str" cm="1">
-        <f t="array" ref="P47">INDEX(_xlfn.TEXTSPLIT($Q47,{","," "}),1)</f>
+        <v>34</v>
+      </c>
+      <c r="L47" t="s">
+        <v>55</v>
+      </c>
+      <c r="M47" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O47" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>164</v>
+      </c>
+      <c r="R47" t="s">
+        <v>165</v>
+      </c>
+      <c r="S47" s="4" t="str" cm="1">
+        <f t="array" ref="S47">INDEX(_xlfn.TEXTSPLIT($T47,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q47" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="32.25">
+      <c r="T47" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="32.25">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B48">
         <v>163</v>
       </c>
       <c r="C48">
         <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="1"/>
         <v>1.63</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>65</v>
       </c>
-      <c r="E48" s="4">
-        <f t="shared" si="1"/>
+      <c r="F48">
+        <f t="shared" si="2"/>
+        <v>143.25</v>
+      </c>
+      <c r="G48" s="4">
+        <f>IF(OR($E48="NA",$B48="NA"),0,$E48/($D48^2))</f>
         <v>24.464601603372351</v>
       </c>
-      <c r="F48" s="4">
-        <f t="shared" si="2"/>
+      <c r="H48" s="4">
+        <f t="shared" si="3"/>
         <v>-8.8654640764629562</v>
       </c>
-      <c r="G48" s="4">
-        <f t="shared" si="3"/>
+      <c r="I48" s="4">
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="H48" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" t="s">
-        <v>164</v>
-      </c>
       <c r="J48" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N48" t="s">
-        <v>165</v>
-      </c>
-      <c r="O48" t="s">
-        <v>166</v>
-      </c>
-      <c r="P48" s="4" t="str" cm="1">
-        <f t="array" ref="P48">INDEX(_xlfn.TEXTSPLIT($Q48,{","," "}),1)</f>
+        <v>167</v>
+      </c>
+      <c r="L48" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" t="s">
+        <v>28</v>
+      </c>
+      <c r="N48" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O48" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>168</v>
+      </c>
+      <c r="R48" t="s">
+        <v>169</v>
+      </c>
+      <c r="S48" s="4" t="str" cm="1">
+        <f t="array" ref="S48">INDEX(_xlfn.TEXTSPLIT($T48,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q48" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="32.25">
+      <c r="T48" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="32.25">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B49">
         <v>188</v>
       </c>
       <c r="C49">
         <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>84</v>
       </c>
-      <c r="E49" s="4">
-        <f t="shared" si="1"/>
+      <c r="F49">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="G49" s="4">
+        <f>IF(OR($E49="NA",$B49="NA"),0,$E49/($D49^2))</f>
         <v>23.766410140334994</v>
       </c>
-      <c r="F49" s="4">
-        <f t="shared" si="2"/>
+      <c r="H49" s="4">
+        <f t="shared" si="3"/>
         <v>-9.5636555395003136</v>
       </c>
-      <c r="G49" s="4">
-        <f t="shared" si="3"/>
+      <c r="I49" s="4">
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="H49" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" t="s">
-        <v>102</v>
-      </c>
       <c r="J49" t="s">
-        <v>40</v>
-      </c>
-      <c r="K49">
+        <v>39</v>
+      </c>
+      <c r="K49" t="s">
+        <v>105</v>
+      </c>
+      <c r="L49" t="s">
+        <v>43</v>
+      </c>
+      <c r="M49">
         <v>72</v>
       </c>
-      <c r="L49">
-        <f t="shared" si="4"/>
+      <c r="N49" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="6"/>
         <v>26280</v>
       </c>
-      <c r="N49" t="s">
-        <v>168</v>
-      </c>
-      <c r="O49" t="s">
-        <v>22</v>
-      </c>
-      <c r="P49" s="4" t="str" cm="1">
-        <f t="array" ref="P49">INDEX(_xlfn.TEXTSPLIT($Q49,{","," "}),1)</f>
+      <c r="Q49" t="s">
+        <v>171</v>
+      </c>
+      <c r="R49" t="s">
+        <v>25</v>
+      </c>
+      <c r="S49" s="4" t="str" cm="1">
+        <f t="array" ref="S49">INDEX(_xlfn.TEXTSPLIT($T49,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="32.25">
+      <c r="T49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="32.25">
       <c r="A50" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B50">
         <v>198</v>
       </c>
       <c r="C50">
         <f t="shared" si="0"/>
+        <v>77.5</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <v>82</v>
       </c>
-      <c r="E50" s="4">
-        <f t="shared" si="1"/>
+      <c r="F50">
+        <f t="shared" si="2"/>
+        <v>180.75</v>
+      </c>
+      <c r="G50" s="4">
+        <f>IF(OR($E50="NA",$B50="NA"),0,$E50/($D50^2))</f>
         <v>20.91623303744516</v>
       </c>
-      <c r="F50" s="4">
-        <f t="shared" si="2"/>
+      <c r="H50" s="4">
+        <f t="shared" si="3"/>
         <v>-12.413832642390147</v>
       </c>
-      <c r="G50" s="4">
-        <f t="shared" si="3"/>
+      <c r="I50" s="4">
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="H50" t="s">
-        <v>37</v>
-      </c>
-      <c r="I50" t="s">
-        <v>90</v>
-      </c>
       <c r="J50" t="s">
-        <v>27</v>
-      </c>
-      <c r="K50">
+        <v>40</v>
+      </c>
+      <c r="K50" t="s">
+        <v>93</v>
+      </c>
+      <c r="L50" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50">
         <v>92</v>
       </c>
-      <c r="L50">
-        <f t="shared" si="4"/>
+      <c r="N50" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="6"/>
         <v>33580</v>
       </c>
-      <c r="N50" t="s">
-        <v>170</v>
-      </c>
-      <c r="O50" t="s">
-        <v>171</v>
-      </c>
-      <c r="P50" s="4" t="str" cm="1">
-        <f t="array" ref="P50">INDEX(_xlfn.TEXTSPLIT($Q50,{","," "}),1)</f>
+      <c r="Q50" t="s">
+        <v>173</v>
+      </c>
+      <c r="R50" t="s">
+        <v>174</v>
+      </c>
+      <c r="S50" s="4" t="str" cm="1">
+        <f t="array" ref="S50">INDEX(_xlfn.TEXTSPLIT($T50,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q50" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="32.25">
+      <c r="T50" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="32.25">
       <c r="A51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B51">
         <v>196</v>
       </c>
       <c r="C51">
         <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="1"/>
         <v>1.96</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <v>87</v>
       </c>
-      <c r="E51" s="4">
-        <f t="shared" si="1"/>
+      <c r="F51">
+        <f t="shared" si="2"/>
+        <v>191.75</v>
+      </c>
+      <c r="G51" s="4">
+        <f>IF(OR($E51="NA",$B51="NA"),0,$E51/($D51^2))</f>
         <v>22.646813827571847</v>
       </c>
-      <c r="F51" s="4">
-        <f t="shared" si="2"/>
+      <c r="H51" s="4">
+        <f t="shared" si="3"/>
         <v>-10.68325185226346</v>
       </c>
-      <c r="G51" s="4">
-        <f t="shared" si="3"/>
+      <c r="I51" s="4">
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="H51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I51" t="s">
-        <v>71</v>
-      </c>
       <c r="J51" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K51" t="s">
-        <v>25</v>
-      </c>
-      <c r="L51" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N51" t="s">
-        <v>173</v>
-      </c>
-      <c r="O51" t="s">
-        <v>174</v>
-      </c>
-      <c r="P51" s="4" t="str" cm="1">
-        <f t="array" ref="P51">INDEX(_xlfn.TEXTSPLIT($Q51,{","," "}),1)</f>
+        <v>74</v>
+      </c>
+      <c r="L51" t="s">
+        <v>55</v>
+      </c>
+      <c r="M51" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O51" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>176</v>
+      </c>
+      <c r="R51" t="s">
+        <v>177</v>
+      </c>
+      <c r="S51" s="4" t="str" cm="1">
+        <f t="array" ref="S51">INDEX(_xlfn.TEXTSPLIT($T51,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="32.25">
+      <c r="T51" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" ht="32.25">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B52">
         <v>171</v>
       </c>
       <c r="C52">
         <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="1"/>
         <v>1.71</v>
       </c>
-      <c r="D52" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="4">
-        <f t="shared" si="1"/>
+      <c r="E52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G52" s="4">
+        <f>IF(OR($E52="NA",$B52="NA"),0,$E52/($D52^2))</f>
         <v>0</v>
       </c>
-      <c r="F52" s="4">
-        <f t="shared" si="2"/>
+      <c r="H52" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G52" s="4">
-        <f t="shared" si="3"/>
+      <c r="I52" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H52" t="s">
-        <v>52</v>
-      </c>
-      <c r="I52" t="s">
-        <v>40</v>
-      </c>
       <c r="J52" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K52" t="s">
-        <v>25</v>
-      </c>
-      <c r="L52" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N52" t="s">
-        <v>176</v>
-      </c>
-      <c r="O52" t="s">
-        <v>150</v>
-      </c>
-      <c r="P52" s="4" t="str" cm="1">
-        <f t="array" ref="P52">INDEX(_xlfn.TEXTSPLIT($Q52,{","," "}),1)</f>
+        <v>43</v>
+      </c>
+      <c r="L52" t="s">
+        <v>43</v>
+      </c>
+      <c r="M52" t="s">
+        <v>28</v>
+      </c>
+      <c r="N52" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O52" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>179</v>
+      </c>
+      <c r="R52" t="s">
+        <v>153</v>
+      </c>
+      <c r="S52" s="4" t="str" cm="1">
+        <f t="array" ref="S52">INDEX(_xlfn.TEXTSPLIT($T52,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q52" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="32.25">
+      <c r="T52" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="32.25">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B53">
         <v>184</v>
       </c>
       <c r="C53">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="1"/>
         <v>1.84</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <v>50</v>
       </c>
-      <c r="E53" s="4">
-        <f t="shared" si="1"/>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="G53" s="4">
+        <f>IF(OR($E53="NA",$B53="NA"),0,$E53/($D53^2))</f>
         <v>14.768431001890358</v>
       </c>
-      <c r="F53" s="4">
-        <f t="shared" si="2"/>
+      <c r="H53" s="4">
+        <f t="shared" si="3"/>
         <v>-18.561634677944951</v>
       </c>
-      <c r="G53" s="4">
-        <f t="shared" si="3"/>
+      <c r="I53" s="4">
+        <f t="shared" si="4"/>
         <v>58</v>
       </c>
-      <c r="H53" t="s">
-        <v>36</v>
-      </c>
-      <c r="I53" t="s">
-        <v>102</v>
-      </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L53" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N53" t="s">
-        <v>130</v>
-      </c>
-      <c r="O53" t="s">
-        <v>179</v>
-      </c>
-      <c r="P53" s="4" t="str" cm="1">
-        <f t="array" ref="P53">INDEX(_xlfn.TEXTSPLIT($Q53,{","," "}),1)</f>
+        <v>105</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" t="s">
+        <v>28</v>
+      </c>
+      <c r="N53" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O53" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>133</v>
+      </c>
+      <c r="R53" t="s">
+        <v>182</v>
+      </c>
+      <c r="S53" s="4" t="str" cm="1">
+        <f t="array" ref="S53">INDEX(_xlfn.TEXTSPLIT($T53,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q53" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="32.25">
+      <c r="T53" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="32.25">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B54">
         <v>188</v>
       </c>
       <c r="C54">
         <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
-      <c r="D54" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="4">
-        <f t="shared" si="1"/>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G54" s="4">
+        <f>IF(OR($E54="NA",$B54="NA"),0,$E54/($D54^2))</f>
         <v>0</v>
       </c>
-      <c r="F54" s="4">
-        <f t="shared" si="2"/>
+      <c r="H54" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G54" s="4">
-        <f t="shared" si="3"/>
+      <c r="I54" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H54" t="s">
-        <v>36</v>
-      </c>
-      <c r="I54" t="s">
-        <v>90</v>
-      </c>
       <c r="J54" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="K54" t="s">
-        <v>25</v>
-      </c>
-      <c r="L54" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N54" t="s">
-        <v>181</v>
-      </c>
-      <c r="O54" t="s">
-        <v>182</v>
-      </c>
-      <c r="P54" s="4" t="str" cm="1">
-        <f t="array" ref="P54">INDEX(_xlfn.TEXTSPLIT($Q54,{","," "}),1)</f>
+        <v>93</v>
+      </c>
+      <c r="L54" t="s">
+        <v>79</v>
+      </c>
+      <c r="M54" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O54" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>184</v>
+      </c>
+      <c r="R54" t="s">
+        <v>185</v>
+      </c>
+      <c r="S54" s="4" t="str" cm="1">
+        <f t="array" ref="S54">INDEX(_xlfn.TEXTSPLIT($T54,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="32.25">
+      <c r="T54" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="32.25">
       <c r="A55" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B55">
         <v>264</v>
       </c>
       <c r="C55">
         <f t="shared" si="0"/>
+        <v>103.5</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="1"/>
         <v>2.64</v>
       </c>
-      <c r="D55" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="4">
-        <f t="shared" si="1"/>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G55" s="4">
+        <f>IF(OR($E55="NA",$B55="NA"),0,$E55/($D55^2))</f>
         <v>0</v>
       </c>
-      <c r="F55" s="4">
-        <f t="shared" si="2"/>
+      <c r="H55" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G55" s="4">
-        <f t="shared" si="3"/>
+      <c r="I55" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H55" t="s">
-        <v>36</v>
-      </c>
-      <c r="I55" t="s">
-        <v>37</v>
-      </c>
       <c r="J55" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K55" t="s">
-        <v>25</v>
-      </c>
-      <c r="L55" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N55" t="s">
-        <v>184</v>
-      </c>
-      <c r="O55" t="s">
-        <v>185</v>
-      </c>
-      <c r="P55" s="4" t="str" cm="1">
-        <f t="array" ref="P55">INDEX(_xlfn.TEXTSPLIT($Q55,{","," "}),1)</f>
+        <v>40</v>
+      </c>
+      <c r="L55" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55" t="s">
+        <v>28</v>
+      </c>
+      <c r="N55" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O55" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>187</v>
+      </c>
+      <c r="R55" t="s">
+        <v>188</v>
+      </c>
+      <c r="S55" s="4" t="str" cm="1">
+        <f t="array" ref="S55">INDEX(_xlfn.TEXTSPLIT($T55,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q55" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="32.25">
+      <c r="T55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="32.25">
       <c r="A56" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B56">
         <v>188</v>
       </c>
       <c r="C56">
         <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="1"/>
         <v>1.88</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <v>80</v>
       </c>
-      <c r="E56" s="4">
-        <f t="shared" si="1"/>
+      <c r="F56">
+        <f t="shared" si="2"/>
+        <v>176.25</v>
+      </c>
+      <c r="G56" s="4">
+        <f>IF(OR($E56="NA",$B56="NA"),0,$E56/($D56^2))</f>
         <v>22.634676324128566</v>
       </c>
-      <c r="F56" s="4">
-        <f t="shared" si="2"/>
+      <c r="H56" s="4">
+        <f t="shared" si="3"/>
         <v>-10.695389355706741</v>
       </c>
-      <c r="G56" s="4">
-        <f t="shared" si="3"/>
+      <c r="I56" s="4">
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="H56" t="s">
-        <v>36</v>
-      </c>
-      <c r="I56" t="s">
-        <v>76</v>
-      </c>
       <c r="J56" t="s">
-        <v>52</v>
-      </c>
-      <c r="K56">
+        <v>39</v>
+      </c>
+      <c r="K56" t="s">
+        <v>79</v>
+      </c>
+      <c r="L56" t="s">
+        <v>55</v>
+      </c>
+      <c r="M56">
         <v>22</v>
       </c>
-      <c r="L56">
-        <f t="shared" si="4"/>
+      <c r="N56" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="6"/>
         <v>8030</v>
       </c>
-      <c r="N56" t="s">
-        <v>187</v>
-      </c>
-      <c r="O56" t="s">
-        <v>188</v>
-      </c>
-      <c r="P56" s="4" t="str" cm="1">
-        <f t="array" ref="P56">INDEX(_xlfn.TEXTSPLIT($Q56,{","," "}),1)</f>
+      <c r="Q56" t="s">
+        <v>190</v>
+      </c>
+      <c r="R56" t="s">
+        <v>191</v>
+      </c>
+      <c r="S56" s="4" t="str" cm="1">
+        <f t="array" ref="S56">INDEX(_xlfn.TEXTSPLIT($T56,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q56" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="32.25">
+      <c r="T56" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" ht="32.25">
       <c r="A57" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B57">
         <v>196</v>
       </c>
       <c r="C57">
         <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="1"/>
         <v>1.96</v>
       </c>
-      <c r="D57" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="4">
-        <f t="shared" si="1"/>
+      <c r="E57" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G57" s="4">
+        <f>IF(OR($E57="NA",$B57="NA"),0,$E57/($D57^2))</f>
         <v>0</v>
       </c>
-      <c r="F57" s="4">
-        <f t="shared" si="2"/>
+      <c r="H57" s="4">
+        <f t="shared" si="3"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G57" s="4">
-        <f t="shared" si="3"/>
+      <c r="I57" s="4">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="H57" t="s">
-        <v>36</v>
-      </c>
-      <c r="I57" t="s">
-        <v>20</v>
-      </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
-      </c>
-      <c r="L57" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N57" t="s">
-        <v>190</v>
-      </c>
-      <c r="O57" t="s">
-        <v>191</v>
-      </c>
-      <c r="P57" s="4" t="str" cm="1">
-        <f t="array" ref="P57">INDEX(_xlfn.TEXTSPLIT($Q57,{","," "}),1)</f>
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" t="s">
+        <v>28</v>
+      </c>
+      <c r="N57" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O57" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>193</v>
+      </c>
+      <c r="R57" t="s">
+        <v>194</v>
+      </c>
+      <c r="S57" s="4" t="str" cm="1">
+        <f t="array" ref="S57">INDEX(_xlfn.TEXTSPLIT($T57,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q57" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="32.25">
+      <c r="T57" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" ht="32.25">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B58">
         <v>185</v>
       </c>
       <c r="C58">
         <f t="shared" si="0"/>
+        <v>72.5</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="1"/>
         <v>1.85</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>85</v>
       </c>
-      <c r="E58" s="4">
-        <f t="shared" si="1"/>
+      <c r="F58">
+        <f t="shared" si="2"/>
+        <v>187.25</v>
+      </c>
+      <c r="G58" s="4">
+        <f>IF(OR($E58="NA",$B58="NA"),0,$E58/($D58^2))</f>
         <v>24.835646457268076</v>
       </c>
-      <c r="F58" s="4">
-        <f t="shared" si="2"/>
+      <c r="H58" s="4">
+        <f t="shared" si="3"/>
         <v>-8.494419222567231</v>
       </c>
-      <c r="G58" s="4">
-        <f t="shared" si="3"/>
+      <c r="I58" s="4">
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
-      <c r="H58" t="s">
-        <v>52</v>
-      </c>
-      <c r="I58" t="s">
-        <v>102</v>
-      </c>
       <c r="J58" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K58" t="s">
+        <v>105</v>
+      </c>
+      <c r="L58" t="s">
+        <v>43</v>
+      </c>
+      <c r="M58" t="s">
+        <v>28</v>
+      </c>
+      <c r="N58" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O58" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>36</v>
+      </c>
+      <c r="R58" t="s">
         <v>25</v>
       </c>
-      <c r="L58" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N58" t="s">
-        <v>33</v>
-      </c>
-      <c r="O58" t="s">
-        <v>22</v>
-      </c>
-      <c r="P58" s="4" t="str" cm="1">
-        <f t="array" ref="P58">INDEX(_xlfn.TEXTSPLIT($Q58,{","," "}),1)</f>
+      <c r="S58" s="4" t="str" cm="1">
+        <f t="array" ref="S58">INDEX(_xlfn.TEXTSPLIT($T58,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q58" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="32.25">
+      <c r="T58" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="32.25">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B59">
         <v>157</v>
       </c>
       <c r="C59">
         <f t="shared" si="0"/>
+        <v>61.5</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="1"/>
         <v>1.57</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G59" s="4">
+        <f>IF(OR($E59="NA",$B59="NA"),0,$E59/($D59^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H59" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K59" t="s">
+        <v>44</v>
+      </c>
+      <c r="L59" t="s">
+        <v>43</v>
+      </c>
+      <c r="M59" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O59" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>36</v>
+      </c>
+      <c r="R59" t="s">
         <v>25</v>
       </c>
-      <c r="E59" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F59" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G59" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H59" t="s">
-        <v>40</v>
-      </c>
-      <c r="I59" t="s">
-        <v>41</v>
-      </c>
-      <c r="J59" t="s">
-        <v>40</v>
-      </c>
-      <c r="K59" t="s">
-        <v>25</v>
-      </c>
-      <c r="L59" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N59" t="s">
-        <v>33</v>
-      </c>
-      <c r="O59" t="s">
-        <v>22</v>
-      </c>
-      <c r="P59" s="4" t="str" cm="1">
-        <f t="array" ref="P59">INDEX(_xlfn.TEXTSPLIT($Q59,{","," "}),1)</f>
+      <c r="S59" s="4" t="str" cm="1">
+        <f t="array" ref="S59">INDEX(_xlfn.TEXTSPLIT($T59,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="32.25">
+      <c r="T59" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" ht="32.25">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B60">
         <v>183</v>
       </c>
       <c r="C60">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G60" s="4">
+        <f>IF(OR($E60="NA",$B60="NA"),0,$E60/($D60^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J60" t="s">
+        <v>43</v>
+      </c>
+      <c r="K60" t="s">
+        <v>22</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60">
+        <v>82</v>
+      </c>
+      <c r="N60" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="6"/>
+        <v>29930</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>24</v>
+      </c>
+      <c r="R60" t="s">
         <v>25</v>
       </c>
-      <c r="E60" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F60" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G60" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H60" t="s">
-        <v>40</v>
-      </c>
-      <c r="I60" t="s">
-        <v>19</v>
-      </c>
-      <c r="J60" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60">
-        <v>82</v>
-      </c>
-      <c r="L60">
-        <f t="shared" si="4"/>
-        <v>29930</v>
-      </c>
-      <c r="N60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" t="s">
-        <v>22</v>
-      </c>
-      <c r="P60" s="4" t="str" cm="1">
-        <f t="array" ref="P60">INDEX(_xlfn.TEXTSPLIT($Q60,{","," "}),1)</f>
+      <c r="S60" s="4" t="str" cm="1">
+        <f t="array" ref="S60">INDEX(_xlfn.TEXTSPLIT($T60,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q60" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="32.25">
+      <c r="T60" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" ht="32.25">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B61">
         <v>183</v>
       </c>
       <c r="C61">
         <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="1"/>
         <v>1.83</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <v>80</v>
       </c>
-      <c r="E61" s="4">
-        <f t="shared" si="1"/>
+      <c r="F61">
+        <f t="shared" si="2"/>
+        <v>176.25</v>
+      </c>
+      <c r="G61" s="4">
+        <f>IF(OR($E61="NA",$B61="NA"),0,$E61/($D61^2))</f>
         <v>23.888440980620498</v>
       </c>
-      <c r="F61" s="4">
-        <f t="shared" si="2"/>
+      <c r="H61" s="4">
+        <f t="shared" si="3"/>
         <v>-9.4416246992148096</v>
       </c>
-      <c r="G61" s="4">
-        <f t="shared" si="3"/>
+      <c r="I61" s="4">
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
-      <c r="H61" t="s">
-        <v>36</v>
-      </c>
-      <c r="I61" t="s">
-        <v>71</v>
-      </c>
       <c r="J61" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K61" t="s">
-        <v>25</v>
-      </c>
-      <c r="L61" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N61" t="s">
-        <v>197</v>
-      </c>
-      <c r="O61" t="s">
-        <v>198</v>
-      </c>
-      <c r="P61" s="4" t="str" cm="1">
-        <f t="array" ref="P61">INDEX(_xlfn.TEXTSPLIT($Q61,{","," "}),1)</f>
+        <v>74</v>
+      </c>
+      <c r="L61" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61" t="s">
+        <v>28</v>
+      </c>
+      <c r="N61" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O61" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>200</v>
+      </c>
+      <c r="R61" t="s">
+        <v>201</v>
+      </c>
+      <c r="S61" s="4" t="str" cm="1">
+        <f t="array" ref="S61">INDEX(_xlfn.TEXTSPLIT($T61,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q61" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="32.25">
+      <c r="T61" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" ht="32.25">
       <c r="A62" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B62">
         <v>170</v>
       </c>
       <c r="C62">
         <f t="shared" si="0"/>
+        <v>66.5</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="1"/>
         <v>1.7</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <v>56.2</v>
       </c>
-      <c r="E62" s="4">
-        <f t="shared" si="1"/>
+      <c r="F62">
+        <f t="shared" si="2"/>
+        <v>123.75</v>
+      </c>
+      <c r="G62" s="4">
+        <f>IF(OR($E62="NA",$B62="NA"),0,$E62/($D62^2))</f>
         <v>19.446366782006923</v>
       </c>
-      <c r="F62" s="4">
-        <f t="shared" si="2"/>
+      <c r="H62" s="4">
+        <f t="shared" si="3"/>
         <v>-13.883698897828385</v>
       </c>
-      <c r="G62" s="4">
-        <f t="shared" si="3"/>
+      <c r="I62" s="4">
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="H62" t="s">
-        <v>52</v>
-      </c>
-      <c r="I62" t="s">
-        <v>27</v>
-      </c>
       <c r="J62" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62">
+        <v>55</v>
+      </c>
+      <c r="K62" t="s">
+        <v>30</v>
+      </c>
+      <c r="L62" t="s">
+        <v>23</v>
+      </c>
+      <c r="M62">
         <v>58</v>
       </c>
-      <c r="L62">
-        <f t="shared" si="4"/>
+      <c r="N62" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="6"/>
         <v>21170</v>
       </c>
-      <c r="N62" t="s">
-        <v>201</v>
-      </c>
-      <c r="O62" t="s">
+      <c r="Q62" t="s">
+        <v>204</v>
+      </c>
+      <c r="R62" t="s">
+        <v>205</v>
+      </c>
+      <c r="S62" s="4" t="str" cm="1">
+        <f t="array" ref="S62">INDEX(_xlfn.TEXTSPLIT($T62,{","," "}),1)</f>
+        <v>Attack of the Clones</v>
+      </c>
+      <c r="T62" t="s">
         <v>202</v>
       </c>
-      <c r="P62" s="4" t="str" cm="1">
-        <f t="array" ref="P62">INDEX(_xlfn.TEXTSPLIT($Q62,{","," "}),1)</f>
-        <v>Attack of the Clones</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="32.25">
+    </row>
+    <row r="63" spans="1:20" ht="32.25">
       <c r="A63" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B63">
         <v>166</v>
       </c>
       <c r="C63">
         <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="1"/>
         <v>1.66</v>
       </c>
-      <c r="D63">
+      <c r="E63">
         <v>50</v>
       </c>
-      <c r="E63" s="4">
-        <f t="shared" si="1"/>
+      <c r="F63">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="G63" s="4">
+        <f>IF(OR($E63="NA",$B63="NA"),0,$E63/($D63^2))</f>
         <v>18.144868631151112</v>
       </c>
-      <c r="F63" s="4">
-        <f t="shared" si="2"/>
+      <c r="H63" s="4">
+        <f t="shared" si="3"/>
         <v>-15.185197048684195</v>
       </c>
-      <c r="G63" s="4">
-        <f t="shared" si="3"/>
+      <c r="I63" s="4">
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="H63" t="s">
-        <v>52</v>
-      </c>
-      <c r="I63" t="s">
-        <v>27</v>
-      </c>
       <c r="J63" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63">
+        <v>55</v>
+      </c>
+      <c r="K63" t="s">
+        <v>30</v>
+      </c>
+      <c r="L63" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63">
         <v>40</v>
       </c>
-      <c r="L63">
-        <f t="shared" si="4"/>
+      <c r="N63" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="6"/>
         <v>14600</v>
       </c>
-      <c r="N63" t="s">
-        <v>201</v>
-      </c>
-      <c r="O63" t="s">
-        <v>202</v>
-      </c>
-      <c r="P63" s="4" t="str" cm="1">
-        <f t="array" ref="P63">INDEX(_xlfn.TEXTSPLIT($Q63,{","," "}),1)</f>
+      <c r="Q63" t="s">
+        <v>204</v>
+      </c>
+      <c r="R63" t="s">
+        <v>205</v>
+      </c>
+      <c r="S63" s="4" t="str" cm="1">
+        <f t="array" ref="S63">INDEX(_xlfn.TEXTSPLIT($T63,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q63" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="32.25">
+      <c r="T63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" ht="32.25">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B64">
         <v>165</v>
       </c>
       <c r="C64">
         <f t="shared" si="0"/>
+        <v>64.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="1"/>
         <v>1.65</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G64" s="4">
+        <f>IF(OR($E64="NA",$B64="NA"),0,$E64/($D64^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I64" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J64" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" t="s">
+        <v>43</v>
+      </c>
+      <c r="M64" t="s">
+        <v>28</v>
+      </c>
+      <c r="N64" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O64" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>36</v>
+      </c>
+      <c r="R64" t="s">
         <v>25</v>
       </c>
-      <c r="E64" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F64" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G64" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H64" t="s">
-        <v>40</v>
-      </c>
-      <c r="I64" t="s">
-        <v>41</v>
-      </c>
-      <c r="J64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K64" t="s">
-        <v>25</v>
-      </c>
-      <c r="L64" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N64" t="s">
-        <v>33</v>
-      </c>
-      <c r="O64" t="s">
-        <v>22</v>
-      </c>
-      <c r="P64" s="4" t="str" cm="1">
-        <f t="array" ref="P64">INDEX(_xlfn.TEXTSPLIT($Q64,{","," "}),1)</f>
+      <c r="S64" s="4" t="str" cm="1">
+        <f t="array" ref="S64">INDEX(_xlfn.TEXTSPLIT($T64,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q64" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="32.25">
+      <c r="T64" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" ht="32.25">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B65">
         <v>193</v>
       </c>
       <c r="C65">
         <f t="shared" si="0"/>
+        <v>75.5</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="1"/>
         <v>1.93</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>80</v>
       </c>
-      <c r="E65" s="4">
-        <f t="shared" si="1"/>
+      <c r="F65">
+        <f t="shared" si="2"/>
+        <v>176.25</v>
+      </c>
+      <c r="G65" s="4">
+        <f>IF(OR($E65="NA",$B65="NA"),0,$E65/($D65^2))</f>
         <v>21.477086633198208</v>
       </c>
-      <c r="F65" s="4">
-        <f t="shared" si="2"/>
+      <c r="H65" s="4">
+        <f t="shared" si="3"/>
         <v>-11.852979046637099</v>
       </c>
-      <c r="G65" s="4">
-        <f t="shared" si="3"/>
+      <c r="I65" s="4">
+        <f t="shared" si="4"/>
         <v>45</v>
-      </c>
-      <c r="H65" t="s">
-        <v>37</v>
-      </c>
-      <c r="I65" t="s">
-        <v>19</v>
       </c>
       <c r="J65" t="s">
         <v>40</v>
       </c>
-      <c r="K65">
+      <c r="K65" t="s">
+        <v>22</v>
+      </c>
+      <c r="L65" t="s">
+        <v>43</v>
+      </c>
+      <c r="M65">
         <v>102</v>
       </c>
-      <c r="L65">
-        <f t="shared" si="4"/>
+      <c r="N65" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="6"/>
         <v>37230</v>
       </c>
-      <c r="N65" t="s">
-        <v>206</v>
-      </c>
-      <c r="O65" t="s">
-        <v>22</v>
-      </c>
-      <c r="P65" s="4" t="str" cm="1">
-        <f t="array" ref="P65">INDEX(_xlfn.TEXTSPLIT($Q65,{","," "}),1)</f>
+      <c r="Q65" t="s">
+        <v>209</v>
+      </c>
+      <c r="R65" t="s">
+        <v>25</v>
+      </c>
+      <c r="S65" s="4" t="str" cm="1">
+        <f t="array" ref="S65">INDEX(_xlfn.TEXTSPLIT($T65,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q65" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="32.25">
+      <c r="T65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" ht="32.25">
       <c r="A66" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B66">
         <v>191</v>
       </c>
       <c r="C66">
         <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="1"/>
         <v>1.91</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G66" s="4">
+        <f>IF(OR($E66="NA",$B66="NA"),0,$E66/($D66^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H66" s="4">
+        <f t="shared" si="3"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I66" s="4">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="J66" t="s">
+        <v>55</v>
+      </c>
+      <c r="K66" t="s">
+        <v>211</v>
+      </c>
+      <c r="L66" t="s">
+        <v>43</v>
+      </c>
+      <c r="M66">
+        <v>67</v>
+      </c>
+      <c r="N66" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="6"/>
+        <v>24455</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>45</v>
+      </c>
+      <c r="R66" t="s">
         <v>25</v>
       </c>
-      <c r="E66" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F66" s="4">
-        <f t="shared" si="2"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G66" s="4">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="H66" t="s">
-        <v>52</v>
-      </c>
-      <c r="I66" t="s">
-        <v>208</v>
-      </c>
-      <c r="J66" t="s">
-        <v>40</v>
-      </c>
-      <c r="K66">
-        <v>67</v>
-      </c>
-      <c r="L66">
-        <f t="shared" si="4"/>
-        <v>24455</v>
-      </c>
-      <c r="N66" t="s">
-        <v>42</v>
-      </c>
-      <c r="O66" t="s">
-        <v>22</v>
-      </c>
-      <c r="P66" s="4" t="str" cm="1">
-        <f t="array" ref="P66">INDEX(_xlfn.TEXTSPLIT($Q66,{","," "}),1)</f>
+      <c r="S66" s="4" t="str" cm="1">
+        <f t="array" ref="S66">INDEX(_xlfn.TEXTSPLIT($T66,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q66" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="32.25">
+      <c r="T66" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" ht="32.25">
       <c r="A67" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B67">
         <v>183</v>
       </c>
       <c r="C67">
-        <f t="shared" ref="C67:C88" si="5">$B67/100</f>
+        <f t="shared" ref="C67:C88" si="7">FLOOR(CONVERT(B67,"cm","in"),0.5)</f>
+        <v>72</v>
+      </c>
+      <c r="D67">
+        <f t="shared" ref="D67:D88" si="8">$B67/100</f>
         <v>1.83</v>
       </c>
-      <c r="D67">
+      <c r="E67">
         <v>79</v>
       </c>
-      <c r="E67" s="4">
-        <f t="shared" ref="E67:E88" si="6">IF(OR($D67="NA",$B67="NA"),0,$D67/($C67^2))</f>
+      <c r="F67">
+        <f t="shared" ref="F67:F88" si="9">FLOOR(CONVERT(E67,"kg","lbm"),0.25)</f>
+        <v>174</v>
+      </c>
+      <c r="G67" s="4">
+        <f>IF(OR($E67="NA",$B67="NA"),0,$E67/($D67^2))</f>
         <v>23.589835468362743</v>
       </c>
-      <c r="F67" s="4">
-        <f t="shared" ref="F67:F88" si="7">$E67-$E$5</f>
+      <c r="H67" s="4">
+        <f t="shared" ref="H67:H88" si="10">$G67-$G$5</f>
         <v>-9.7402302114725643</v>
       </c>
-      <c r="G67" s="4">
-        <f t="shared" ref="G67:G88" si="8">RANK($E67,$E$2:$E$88)</f>
+      <c r="I67" s="4">
+        <f t="shared" ref="I67:I88" si="11">RANK($G67,$G$2:$G$88)</f>
         <v>37</v>
       </c>
-      <c r="H67" t="s">
-        <v>52</v>
-      </c>
-      <c r="I67" t="s">
-        <v>208</v>
-      </c>
       <c r="J67" t="s">
-        <v>40</v>
-      </c>
-      <c r="K67">
+        <v>55</v>
+      </c>
+      <c r="K67" t="s">
+        <v>211</v>
+      </c>
+      <c r="L67" t="s">
+        <v>43</v>
+      </c>
+      <c r="M67">
         <v>66</v>
       </c>
-      <c r="L67">
-        <f t="shared" ref="L67:L88" si="9">$K67*365</f>
+      <c r="N67" t="b">
+        <f t="shared" ref="N67:N88" si="12">ISNUMBER(M67)</f>
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <f t="shared" ref="O67:O88" si="13">$M67*365</f>
         <v>24090</v>
       </c>
-      <c r="N67" t="s">
-        <v>210</v>
-      </c>
-      <c r="O67" t="s">
-        <v>22</v>
-      </c>
-      <c r="P67" s="4" t="str" cm="1">
-        <f t="array" ref="P67">INDEX(_xlfn.TEXTSPLIT($Q67,{","," "}),1)</f>
+      <c r="Q67" t="s">
+        <v>213</v>
+      </c>
+      <c r="R67" t="s">
+        <v>25</v>
+      </c>
+      <c r="S67" s="4" t="str" cm="1">
+        <f t="array" ref="S67">INDEX(_xlfn.TEXTSPLIT($T67,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q67" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="32.25">
+      <c r="T67" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" ht="32.25">
       <c r="A68" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B68">
         <v>168</v>
       </c>
       <c r="C68">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>66</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="8"/>
         <v>1.68</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>55</v>
       </c>
-      <c r="E68" s="4">
-        <f t="shared" si="6"/>
+      <c r="F68">
+        <f t="shared" si="9"/>
+        <v>121.25</v>
+      </c>
+      <c r="G68" s="4">
+        <f>IF(OR($E68="NA",$B68="NA"),0,$E68/($D68^2))</f>
         <v>19.486961451247168</v>
       </c>
-      <c r="F68" s="4">
-        <f t="shared" si="7"/>
+      <c r="H68" s="4">
+        <f t="shared" si="10"/>
         <v>-13.843104228588139</v>
       </c>
-      <c r="G68" s="4">
-        <f t="shared" si="8"/>
+      <c r="I68" s="4">
+        <f t="shared" si="11"/>
         <v>47</v>
       </c>
-      <c r="H68" t="s">
-        <v>212</v>
-      </c>
-      <c r="I68" t="s">
-        <v>213</v>
-      </c>
       <c r="J68" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="K68" t="s">
-        <v>25</v>
-      </c>
-      <c r="L68" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N68" t="s">
-        <v>214</v>
-      </c>
-      <c r="O68" t="s">
-        <v>215</v>
-      </c>
-      <c r="P68" s="4" t="str" cm="1">
-        <f t="array" ref="P68">INDEX(_xlfn.TEXTSPLIT($Q68,{","," "}),1)</f>
+        <v>216</v>
+      </c>
+      <c r="L68" t="s">
+        <v>30</v>
+      </c>
+      <c r="M68" t="s">
+        <v>28</v>
+      </c>
+      <c r="N68" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O68" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>217</v>
+      </c>
+      <c r="R68" t="s">
+        <v>218</v>
+      </c>
+      <c r="S68" s="4" t="str" cm="1">
+        <f t="array" ref="S68">INDEX(_xlfn.TEXTSPLIT($T68,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q68" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="32.25">
+      <c r="T68" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" ht="32.25">
       <c r="A69" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B69">
         <v>198</v>
       </c>
       <c r="C69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>77.5</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="8"/>
         <v>1.98</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>102</v>
       </c>
-      <c r="E69" s="4">
-        <f t="shared" si="6"/>
+      <c r="F69">
+        <f t="shared" si="9"/>
+        <v>224.75</v>
+      </c>
+      <c r="G69" s="4">
+        <f>IF(OR($E69="NA",$B69="NA"),0,$E69/($D69^2))</f>
         <v>26.017753290480563</v>
       </c>
-      <c r="F69" s="4">
-        <f t="shared" si="7"/>
+      <c r="H69" s="4">
+        <f t="shared" si="10"/>
         <v>-7.3123123893547444</v>
       </c>
-      <c r="G69" s="4">
-        <f t="shared" si="8"/>
+      <c r="I69" s="4">
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="H69" t="s">
-        <v>36</v>
-      </c>
-      <c r="I69" t="s">
-        <v>40</v>
-      </c>
       <c r="J69" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="K69" t="s">
-        <v>25</v>
-      </c>
-      <c r="L69" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N69" t="s">
-        <v>217</v>
-      </c>
-      <c r="O69" t="s">
-        <v>218</v>
-      </c>
-      <c r="P69" s="4" t="str" cm="1">
-        <f t="array" ref="P69">INDEX(_xlfn.TEXTSPLIT($Q69,{","," "}),1)</f>
+        <v>43</v>
+      </c>
+      <c r="L69" t="s">
+        <v>30</v>
+      </c>
+      <c r="M69" t="s">
+        <v>28</v>
+      </c>
+      <c r="N69" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O69" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>220</v>
+      </c>
+      <c r="R69" t="s">
+        <v>221</v>
+      </c>
+      <c r="S69" s="4" t="str" cm="1">
+        <f t="array" ref="S69">INDEX(_xlfn.TEXTSPLIT($T69,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q69" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="32.25">
+      <c r="T69" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" ht="32.25">
       <c r="A70" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B70">
         <v>229</v>
       </c>
       <c r="C70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="8"/>
         <v>2.29</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>88</v>
       </c>
-      <c r="E70" s="4">
-        <f t="shared" si="6"/>
+      <c r="F70">
+        <f t="shared" si="9"/>
+        <v>194</v>
+      </c>
+      <c r="G70" s="4">
+        <f>IF(OR($E70="NA",$B70="NA"),0,$E70/($D70^2))</f>
         <v>16.780763143342039</v>
       </c>
-      <c r="F70" s="4">
-        <f t="shared" si="7"/>
+      <c r="H70" s="4">
+        <f t="shared" si="10"/>
         <v>-16.549302536493268</v>
       </c>
-      <c r="G70" s="4">
-        <f t="shared" si="8"/>
+      <c r="I70" s="4">
+        <f t="shared" si="11"/>
         <v>54</v>
       </c>
-      <c r="H70" t="s">
-        <v>36</v>
-      </c>
-      <c r="I70" t="s">
-        <v>89</v>
-      </c>
       <c r="J70" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K70" t="s">
-        <v>25</v>
-      </c>
-      <c r="L70" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N70" t="s">
-        <v>93</v>
-      </c>
-      <c r="O70" t="s">
-        <v>220</v>
-      </c>
-      <c r="P70" s="4" t="str" cm="1">
-        <f t="array" ref="P70">INDEX(_xlfn.TEXTSPLIT($Q70,{","," "}),1)</f>
+        <v>92</v>
+      </c>
+      <c r="L70" t="s">
+        <v>55</v>
+      </c>
+      <c r="M70" t="s">
+        <v>28</v>
+      </c>
+      <c r="N70" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O70" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>96</v>
+      </c>
+      <c r="R70" t="s">
+        <v>223</v>
+      </c>
+      <c r="S70" s="4" t="str" cm="1">
+        <f t="array" ref="S70">INDEX(_xlfn.TEXTSPLIT($T70,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q70" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="32.25">
+      <c r="T70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" ht="32.25">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B71">
         <v>213</v>
       </c>
       <c r="C71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>83.5</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="8"/>
         <v>2.13</v>
       </c>
-      <c r="D71" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="4">
-        <f t="shared" si="6"/>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G71" s="4">
+        <f>IF(OR($E71="NA",$B71="NA"),0,$E71/($D71^2))</f>
         <v>0</v>
       </c>
-      <c r="F71" s="4">
-        <f t="shared" si="7"/>
+      <c r="H71" s="4">
+        <f t="shared" si="10"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G71" s="4">
-        <f t="shared" si="8"/>
+      <c r="I71" s="4">
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="H71" t="s">
-        <v>36</v>
-      </c>
-      <c r="I71" t="s">
-        <v>89</v>
-      </c>
       <c r="J71" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K71" t="s">
-        <v>25</v>
-      </c>
-      <c r="L71" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N71" t="s">
-        <v>93</v>
-      </c>
-      <c r="O71" t="s">
-        <v>220</v>
-      </c>
-      <c r="P71" s="4" t="str" cm="1">
-        <f t="array" ref="P71">INDEX(_xlfn.TEXTSPLIT($Q71,{","," "}),1)</f>
+        <v>92</v>
+      </c>
+      <c r="L71" t="s">
+        <v>55</v>
+      </c>
+      <c r="M71" t="s">
+        <v>28</v>
+      </c>
+      <c r="N71" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O71" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>96</v>
+      </c>
+      <c r="R71" t="s">
+        <v>223</v>
+      </c>
+      <c r="S71" s="4" t="str" cm="1">
+        <f t="array" ref="S71">INDEX(_xlfn.TEXTSPLIT($T71,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q71" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="32.25">
+      <c r="T71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" ht="32.25">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B72">
         <v>167</v>
       </c>
       <c r="C72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>65.5</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="8"/>
         <v>1.67</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G72" s="4">
+        <f>IF(OR($E72="NA",$B72="NA"),0,$E72/($D72^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="4">
+        <f t="shared" si="10"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I72" s="4">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="J72" t="s">
+        <v>40</v>
+      </c>
+      <c r="K72" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" t="s">
+        <v>28</v>
+      </c>
+      <c r="N72" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O72" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>133</v>
+      </c>
+      <c r="R72" t="s">
         <v>25</v>
       </c>
-      <c r="E72" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F72" s="4">
-        <f t="shared" si="7"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G72" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="H72" t="s">
-        <v>37</v>
-      </c>
-      <c r="I72" t="s">
-        <v>19</v>
-      </c>
-      <c r="J72" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" t="s">
-        <v>25</v>
-      </c>
-      <c r="L72" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N72" t="s">
-        <v>130</v>
-      </c>
-      <c r="O72" t="s">
-        <v>22</v>
-      </c>
-      <c r="P72" s="4" t="str" cm="1">
-        <f t="array" ref="P72">INDEX(_xlfn.TEXTSPLIT($Q72,{","," "}),1)</f>
+      <c r="S72" s="4" t="str" cm="1">
+        <f t="array" ref="S72">INDEX(_xlfn.TEXTSPLIT($T72,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q72" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="32.25">
+      <c r="T72" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" ht="32.25">
       <c r="A73" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B73">
         <v>79</v>
       </c>
       <c r="C73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>31</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="8"/>
         <v>0.79</v>
       </c>
-      <c r="D73">
+      <c r="E73">
         <v>15</v>
       </c>
-      <c r="E73" s="4">
-        <f t="shared" si="6"/>
+      <c r="F73">
+        <f t="shared" si="9"/>
+        <v>33</v>
+      </c>
+      <c r="G73" s="4">
+        <f>IF(OR($E73="NA",$B73="NA"),0,$E73/($D73^2))</f>
         <v>24.034609838166958</v>
       </c>
-      <c r="F73" s="4">
-        <f t="shared" si="7"/>
+      <c r="H73" s="4">
+        <f t="shared" si="10"/>
         <v>-9.2954558416683497</v>
       </c>
-      <c r="G73" s="4">
-        <f t="shared" si="8"/>
+      <c r="I73" s="4">
+        <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="H73" t="s">
-        <v>36</v>
-      </c>
-      <c r="I73" t="s">
-        <v>224</v>
-      </c>
       <c r="J73" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K73" t="s">
-        <v>25</v>
-      </c>
-      <c r="L73" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N73" t="s">
-        <v>225</v>
-      </c>
-      <c r="O73" t="s">
-        <v>226</v>
-      </c>
-      <c r="P73" s="4" t="str" cm="1">
-        <f t="array" ref="P73">INDEX(_xlfn.TEXTSPLIT($Q73,{","," "}),1)</f>
+        <v>227</v>
+      </c>
+      <c r="L73" t="s">
+        <v>67</v>
+      </c>
+      <c r="M73" t="s">
+        <v>28</v>
+      </c>
+      <c r="N73" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O73" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>228</v>
+      </c>
+      <c r="R73" t="s">
+        <v>229</v>
+      </c>
+      <c r="S73" s="4" t="str" cm="1">
+        <f t="array" ref="S73">INDEX(_xlfn.TEXTSPLIT($T73,{","," "}),1)</f>
         <v>The Phantom Menace</v>
       </c>
-      <c r="Q73" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="32.25">
+      <c r="T73" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" ht="32.25">
       <c r="A74" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B74">
         <v>96</v>
       </c>
       <c r="C74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>37.5</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="8"/>
         <v>0.96</v>
       </c>
-      <c r="D74" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="4">
-        <f t="shared" si="6"/>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G74" s="4">
+        <f>IF(OR($E74="NA",$B74="NA"),0,$E74/($D74^2))</f>
         <v>0</v>
       </c>
-      <c r="F74" s="4">
-        <f t="shared" si="7"/>
+      <c r="H74" s="4">
+        <f t="shared" si="10"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G74" s="4">
-        <f t="shared" si="8"/>
+      <c r="I74" s="4">
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="H74" t="s">
-        <v>36</v>
-      </c>
-      <c r="I74" t="s">
-        <v>228</v>
-      </c>
       <c r="J74" t="s">
-        <v>229</v>
+        <v>39</v>
       </c>
       <c r="K74" t="s">
-        <v>25</v>
-      </c>
-      <c r="L74" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N74" t="s">
-        <v>25</v>
-      </c>
-      <c r="O74" t="s">
-        <v>25</v>
-      </c>
-      <c r="P74" s="4" t="str" cm="1">
-        <f t="array" ref="P74">INDEX(_xlfn.TEXTSPLIT($Q74,{","," "}),1)</f>
+        <v>231</v>
+      </c>
+      <c r="L74" t="s">
+        <v>232</v>
+      </c>
+      <c r="M74" t="s">
+        <v>28</v>
+      </c>
+      <c r="N74" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O74" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>28</v>
+      </c>
+      <c r="R74" t="s">
+        <v>28</v>
+      </c>
+      <c r="S74" s="4" t="str" cm="1">
+        <f t="array" ref="S74">INDEX(_xlfn.TEXTSPLIT($T74,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q74" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="32.25">
+      <c r="T74" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" ht="32.25">
       <c r="A75" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B75">
         <v>193</v>
       </c>
       <c r="C75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>75.5</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="8"/>
         <v>1.93</v>
       </c>
-      <c r="D75">
+      <c r="E75">
         <v>48</v>
       </c>
-      <c r="E75" s="4">
-        <f t="shared" si="6"/>
+      <c r="F75">
+        <f t="shared" si="9"/>
+        <v>105.75</v>
+      </c>
+      <c r="G75" s="4">
+        <f>IF(OR($E75="NA",$B75="NA"),0,$E75/($D75^2))</f>
         <v>12.886251979918924</v>
       </c>
-      <c r="F75" s="4">
-        <f t="shared" si="7"/>
+      <c r="H75" s="4">
+        <f t="shared" si="10"/>
         <v>-20.443813699916383</v>
       </c>
-      <c r="G75" s="4">
-        <f t="shared" si="8"/>
+      <c r="I75" s="4">
+        <f t="shared" si="11"/>
         <v>59</v>
       </c>
-      <c r="H75" t="s">
-        <v>36</v>
-      </c>
-      <c r="I75" t="s">
-        <v>231</v>
-      </c>
       <c r="J75" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K75" t="s">
-        <v>25</v>
-      </c>
-      <c r="L75" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N75" t="s">
-        <v>232</v>
-      </c>
-      <c r="O75" t="s">
-        <v>233</v>
-      </c>
-      <c r="P75" s="4" t="str" cm="1">
-        <f t="array" ref="P75">INDEX(_xlfn.TEXTSPLIT($Q75,{","," "}),1)</f>
+        <v>234</v>
+      </c>
+      <c r="L75" t="s">
+        <v>67</v>
+      </c>
+      <c r="M75" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O75" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>235</v>
+      </c>
+      <c r="R75" t="s">
+        <v>236</v>
+      </c>
+      <c r="S75" s="4" t="str" cm="1">
+        <f t="array" ref="S75">INDEX(_xlfn.TEXTSPLIT($T75,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q75" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="32.25">
+      <c r="T75" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="32.25">
       <c r="A76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B76">
         <v>191</v>
       </c>
       <c r="C76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>75</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="8"/>
         <v>1.91</v>
       </c>
-      <c r="D76" t="s">
-        <v>25</v>
-      </c>
-      <c r="E76" s="4">
-        <f t="shared" si="6"/>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G76" s="4">
+        <f>IF(OR($E76="NA",$B76="NA"),0,$E76/($D76^2))</f>
         <v>0</v>
       </c>
-      <c r="F76" s="4">
-        <f t="shared" si="7"/>
+      <c r="H76" s="4">
+        <f t="shared" si="10"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G76" s="4">
-        <f t="shared" si="8"/>
+      <c r="I76" s="4">
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="H76" t="s">
-        <v>36</v>
-      </c>
-      <c r="I76" t="s">
-        <v>89</v>
-      </c>
       <c r="J76" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="K76" t="s">
-        <v>25</v>
-      </c>
-      <c r="L76" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N76" t="s">
-        <v>235</v>
-      </c>
-      <c r="O76" t="s">
-        <v>236</v>
-      </c>
-      <c r="P76" s="4" t="str" cm="1">
-        <f t="array" ref="P76">INDEX(_xlfn.TEXTSPLIT($Q76,{","," "}),1)</f>
+        <v>92</v>
+      </c>
+      <c r="L76" t="s">
+        <v>29</v>
+      </c>
+      <c r="M76" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O76" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>238</v>
+      </c>
+      <c r="R76" t="s">
+        <v>239</v>
+      </c>
+      <c r="S76" s="4" t="str" cm="1">
+        <f t="array" ref="S76">INDEX(_xlfn.TEXTSPLIT($T76,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q76" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="32.25">
+      <c r="T76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" ht="32.25">
       <c r="A77" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B77">
         <v>178</v>
       </c>
       <c r="C77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>70</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="8"/>
         <v>1.78</v>
       </c>
-      <c r="D77">
+      <c r="E77">
         <v>57</v>
       </c>
-      <c r="E77" s="4">
-        <f t="shared" si="6"/>
+      <c r="F77">
+        <f t="shared" si="9"/>
+        <v>125.5</v>
+      </c>
+      <c r="G77" s="4">
+        <f>IF(OR($E77="NA",$B77="NA"),0,$E77/($D77^2))</f>
         <v>17.99015275849009</v>
       </c>
-      <c r="F77" s="4">
-        <f t="shared" si="7"/>
+      <c r="H77" s="4">
+        <f t="shared" si="10"/>
         <v>-15.339912921345217</v>
       </c>
-      <c r="G77" s="4">
-        <f t="shared" si="8"/>
+      <c r="I77" s="4">
+        <f t="shared" si="11"/>
         <v>51</v>
       </c>
-      <c r="H77" t="s">
-        <v>36</v>
-      </c>
-      <c r="I77" t="s">
-        <v>238</v>
-      </c>
       <c r="J77" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="K77" t="s">
-        <v>25</v>
-      </c>
-      <c r="L77" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N77" t="s">
-        <v>239</v>
-      </c>
-      <c r="O77" t="s">
-        <v>240</v>
-      </c>
-      <c r="P77" s="4" t="str" cm="1">
-        <f t="array" ref="P77">INDEX(_xlfn.TEXTSPLIT($Q77,{","," "}),1)</f>
+        <v>241</v>
+      </c>
+      <c r="L77" t="s">
+        <v>55</v>
+      </c>
+      <c r="M77" t="s">
+        <v>28</v>
+      </c>
+      <c r="N77" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O77" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>242</v>
+      </c>
+      <c r="R77" t="s">
+        <v>243</v>
+      </c>
+      <c r="S77" s="4" t="str" cm="1">
+        <f t="array" ref="S77">INDEX(_xlfn.TEXTSPLIT($T77,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q77" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="32.25">
+      <c r="T77" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" ht="32.25">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B78">
         <v>216</v>
       </c>
       <c r="C78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>85</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="8"/>
         <v>2.16</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>159</v>
       </c>
-      <c r="E78" s="4">
-        <f t="shared" si="6"/>
+      <c r="F78">
+        <f t="shared" si="9"/>
+        <v>350.5</v>
+      </c>
+      <c r="G78" s="4">
+        <f>IF(OR($E78="NA",$B78="NA"),0,$E78/($D78^2))</f>
         <v>34.079218106995881</v>
       </c>
-      <c r="F78" s="4">
-        <f t="shared" si="7"/>
+      <c r="H78" s="4">
+        <f t="shared" si="10"/>
         <v>0.74915242716057406</v>
       </c>
-      <c r="G78" s="4">
-        <f t="shared" si="8"/>
+      <c r="I78" s="4">
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="H78" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78" t="s">
-        <v>242</v>
-      </c>
       <c r="J78" t="s">
-        <v>243</v>
+        <v>39</v>
       </c>
       <c r="K78" t="s">
-        <v>25</v>
-      </c>
-      <c r="L78" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N78" t="s">
-        <v>244</v>
-      </c>
-      <c r="O78" t="s">
         <v>245</v>
       </c>
-      <c r="P78" s="4" t="str" cm="1">
-        <f t="array" ref="P78">INDEX(_xlfn.TEXTSPLIT($Q78,{","," "}),1)</f>
+      <c r="L78" t="s">
+        <v>246</v>
+      </c>
+      <c r="M78" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O78" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>247</v>
+      </c>
+      <c r="R78" t="s">
+        <v>248</v>
+      </c>
+      <c r="S78" s="4" t="str" cm="1">
+        <f t="array" ref="S78">INDEX(_xlfn.TEXTSPLIT($T78,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q78" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="32.25">
+      <c r="T78" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="32.25">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B79">
         <v>234</v>
       </c>
       <c r="C79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>92</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="8"/>
         <v>2.34</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>136</v>
       </c>
-      <c r="E79" s="4">
-        <f t="shared" si="6"/>
+      <c r="F79">
+        <f t="shared" si="9"/>
+        <v>299.75</v>
+      </c>
+      <c r="G79" s="4">
+        <f>IF(OR($E79="NA",$B79="NA"),0,$E79/($D79^2))</f>
         <v>24.837460734896638</v>
       </c>
-      <c r="F79" s="4">
-        <f t="shared" si="7"/>
+      <c r="H79" s="4">
+        <f t="shared" si="10"/>
         <v>-8.4926049449386696</v>
       </c>
-      <c r="G79" s="4">
-        <f t="shared" si="8"/>
+      <c r="I79" s="4">
+        <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="H79" t="s">
-        <v>40</v>
-      </c>
-      <c r="I79" t="s">
-        <v>40</v>
-      </c>
       <c r="J79" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K79" t="s">
-        <v>25</v>
-      </c>
-      <c r="L79" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N79" t="s">
-        <v>65</v>
-      </c>
-      <c r="O79" t="s">
-        <v>66</v>
-      </c>
-      <c r="P79" s="4" t="str" cm="1">
-        <f t="array" ref="P79">INDEX(_xlfn.TEXTSPLIT($Q79,{","," "}),1)</f>
+        <v>43</v>
+      </c>
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O79" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>68</v>
+      </c>
+      <c r="R79" t="s">
+        <v>69</v>
+      </c>
+      <c r="S79" s="4" t="str" cm="1">
+        <f t="array" ref="S79">INDEX(_xlfn.TEXTSPLIT($T79,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q79" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="32.25">
+      <c r="T79" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="32.25">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B80">
         <v>188</v>
       </c>
       <c r="C80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>74</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="8"/>
         <v>1.88</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>79</v>
       </c>
-      <c r="E80" s="4">
-        <f t="shared" si="6"/>
+      <c r="F80">
+        <f t="shared" si="9"/>
+        <v>174</v>
+      </c>
+      <c r="G80" s="4">
+        <f>IF(OR($E80="NA",$B80="NA"),0,$E80/($D80^2))</f>
         <v>22.351742870076958</v>
       </c>
-      <c r="F80" s="4">
-        <f t="shared" si="7"/>
+      <c r="H80" s="4">
+        <f t="shared" si="10"/>
         <v>-10.97832280975835</v>
       </c>
-      <c r="G80" s="4">
-        <f t="shared" si="8"/>
+      <c r="I80" s="4">
+        <f t="shared" si="11"/>
         <v>42</v>
       </c>
-      <c r="H80" t="s">
-        <v>40</v>
-      </c>
-      <c r="I80" t="s">
-        <v>41</v>
-      </c>
       <c r="J80" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K80" t="s">
+        <v>44</v>
+      </c>
+      <c r="L80" t="s">
+        <v>43</v>
+      </c>
+      <c r="M80" t="s">
+        <v>28</v>
+      </c>
+      <c r="N80" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O80" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>45</v>
+      </c>
+      <c r="R80" t="s">
         <v>25</v>
       </c>
-      <c r="L80" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N80" t="s">
-        <v>42</v>
-      </c>
-      <c r="O80" t="s">
-        <v>22</v>
-      </c>
-      <c r="P80" s="4" t="str" cm="1">
-        <f t="array" ref="P80">INDEX(_xlfn.TEXTSPLIT($Q80,{","," "}),1)</f>
+      <c r="S80" s="4" t="str" cm="1">
+        <f t="array" ref="S80">INDEX(_xlfn.TEXTSPLIT($T80,{","," "}),1)</f>
         <v>Revenge of the Sith</v>
       </c>
-      <c r="Q80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="32.25">
+      <c r="T80" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="32.25">
       <c r="A81" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B81">
         <v>178</v>
       </c>
       <c r="C81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>70</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="8"/>
         <v>1.78</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>48</v>
       </c>
-      <c r="E81" s="4">
-        <f t="shared" si="6"/>
+      <c r="F81">
+        <f t="shared" si="9"/>
+        <v>105.75</v>
+      </c>
+      <c r="G81" s="4">
+        <f>IF(OR($E81="NA",$B81="NA"),0,$E81/($D81^2))</f>
         <v>15.149602322939023</v>
       </c>
-      <c r="F81" s="4">
-        <f t="shared" si="7"/>
+      <c r="H81" s="4">
+        <f t="shared" si="10"/>
         <v>-18.180463356896283</v>
       </c>
-      <c r="G81" s="4">
-        <f t="shared" si="8"/>
+      <c r="I81" s="4">
+        <f t="shared" si="11"/>
         <v>57</v>
       </c>
-      <c r="H81" t="s">
-        <v>36</v>
-      </c>
-      <c r="I81" t="s">
-        <v>90</v>
-      </c>
       <c r="J81" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K81" t="s">
-        <v>25</v>
-      </c>
-      <c r="L81" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N81" t="s">
-        <v>250</v>
-      </c>
-      <c r="O81" t="s">
-        <v>25</v>
-      </c>
-      <c r="P81" s="4" t="str" cm="1">
-        <f t="array" ref="P81">INDEX(_xlfn.TEXTSPLIT($Q81,{","," "}),1)</f>
+        <v>93</v>
+      </c>
+      <c r="L81" t="s">
+        <v>40</v>
+      </c>
+      <c r="M81" t="s">
+        <v>28</v>
+      </c>
+      <c r="N81" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O81" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>253</v>
+      </c>
+      <c r="R81" t="s">
+        <v>28</v>
+      </c>
+      <c r="S81" s="4" t="str" cm="1">
+        <f t="array" ref="S81">INDEX(_xlfn.TEXTSPLIT($T81,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q81" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="32.25">
+      <c r="T81" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" ht="32.25">
       <c r="A82" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B82">
         <v>206</v>
       </c>
       <c r="C82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>81</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="8"/>
         <v>2.06</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>80</v>
       </c>
-      <c r="E82" s="4">
-        <f t="shared" si="6"/>
+      <c r="F82">
+        <f t="shared" si="9"/>
+        <v>176.25</v>
+      </c>
+      <c r="G82" s="4">
+        <f>IF(OR($E82="NA",$B82="NA"),0,$E82/($D82^2))</f>
         <v>18.851918182675089</v>
       </c>
-      <c r="F82" s="4">
+      <c r="H82" s="4">
+        <f t="shared" si="10"/>
+        <v>-14.478147497160219</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="11"/>
+        <v>49</v>
+      </c>
+      <c r="J82" t="s">
+        <v>39</v>
+      </c>
+      <c r="K82" t="s">
+        <v>92</v>
+      </c>
+      <c r="L82" t="s">
+        <v>55</v>
+      </c>
+      <c r="M82" t="s">
+        <v>28</v>
+      </c>
+      <c r="N82" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O82" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>255</v>
+      </c>
+      <c r="R82" t="s">
+        <v>256</v>
+      </c>
+      <c r="S82" s="4" t="str" cm="1">
+        <f t="array" ref="S82">INDEX(_xlfn.TEXTSPLIT($T82,{","," "}),1)</f>
+        <v>Revenge of the Sith</v>
+      </c>
+      <c r="T82" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" ht="32.25">
+      <c r="A83" t="s">
+        <v>257</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="e">
         <f t="shared" si="7"/>
-        <v>-14.478147497160219</v>
-      </c>
-      <c r="G82" s="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D83" t="e">
         <f t="shared" si="8"/>
-        <v>49</v>
-      </c>
-      <c r="H82" t="s">
-        <v>36</v>
-      </c>
-      <c r="I82" t="s">
-        <v>89</v>
-      </c>
-      <c r="J82" t="s">
-        <v>52</v>
-      </c>
-      <c r="K82" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G83" s="4">
+        <f>IF(OR($E83="NA",$B83="NA"),0,$E83/($D83^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="4">
+        <f t="shared" si="10"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I83" s="4">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="J83" t="s">
+        <v>55</v>
+      </c>
+      <c r="K83" t="s">
+        <v>105</v>
+      </c>
+      <c r="L83" t="s">
+        <v>105</v>
+      </c>
+      <c r="M83" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O83" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>28</v>
+      </c>
+      <c r="R83" t="s">
         <v>25</v>
       </c>
-      <c r="L82" t="e">
+      <c r="S83" s="4" t="str" cm="1">
+        <f t="array" ref="S83">INDEX(_xlfn.TEXTSPLIT($T83,{","," "}),1)</f>
+        <v>The Force Awakens</v>
+      </c>
+      <c r="T83" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" ht="32.25">
+      <c r="A84" t="s">
+        <v>259</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D84" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E84" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" t="e">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
-      <c r="N82" t="s">
-        <v>252</v>
-      </c>
-      <c r="O82" t="s">
-        <v>253</v>
-      </c>
-      <c r="P82" s="4" t="str" cm="1">
-        <f t="array" ref="P82">INDEX(_xlfn.TEXTSPLIT($Q82,{","," "}),1)</f>
-        <v>Revenge of the Sith</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="32.25">
-      <c r="A83" t="s">
-        <v>254</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="G84" s="4">
+        <f>IF(OR($E84="NA",$B84="NA"),0,$E84/($D84^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="4">
+        <f t="shared" si="10"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I84" s="4">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="J84" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" t="s">
+        <v>44</v>
+      </c>
+      <c r="L84" t="s">
+        <v>84</v>
+      </c>
+      <c r="M84" t="s">
+        <v>28</v>
+      </c>
+      <c r="N84" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O84" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>28</v>
+      </c>
+      <c r="R84" t="s">
         <v>25</v>
       </c>
-      <c r="C83" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="S84" s="4" t="str" cm="1">
+        <f t="array" ref="S84">INDEX(_xlfn.TEXTSPLIT($T84,{","," "}),1)</f>
+        <v>The Force Awakens</v>
+      </c>
+      <c r="T84" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" ht="32.25">
+      <c r="A85" t="s">
+        <v>260</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D85" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E85" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G85" s="4">
+        <f>IF(OR($E85="NA",$B85="NA"),0,$E85/($D85^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="4">
+        <f t="shared" si="10"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I85" s="4">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="J85" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" t="s">
+        <v>44</v>
+      </c>
+      <c r="L85" t="s">
+        <v>43</v>
+      </c>
+      <c r="M85" t="s">
+        <v>28</v>
+      </c>
+      <c r="N85" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O85" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>28</v>
+      </c>
+      <c r="R85" t="s">
         <v>25</v>
       </c>
-      <c r="E83" s="4">
-        <f t="shared" si="6"/>
+      <c r="S85" s="4" t="str" cm="1">
+        <f t="array" ref="S85">INDEX(_xlfn.TEXTSPLIT($T85,{","," "}),1)</f>
+        <v>The Force Awakens</v>
+      </c>
+      <c r="T85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" ht="32.25">
+      <c r="A86" t="s">
+        <v>261</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" t="e">
+        <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D86" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E86" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G86" s="4">
+        <f>IF(OR($E86="NA",$B86="NA"),0,$E86/($D86^2))</f>
         <v>0</v>
       </c>
-      <c r="F83" s="4">
+      <c r="H86" s="4">
+        <f t="shared" si="10"/>
+        <v>-33.330065679835307</v>
+      </c>
+      <c r="I86" s="4">
+        <f t="shared" si="11"/>
+        <v>60</v>
+      </c>
+      <c r="J86" t="s">
+        <v>39</v>
+      </c>
+      <c r="K86" t="s">
+        <v>39</v>
+      </c>
+      <c r="L86" t="s">
+        <v>55</v>
+      </c>
+      <c r="M86" t="s">
+        <v>28</v>
+      </c>
+      <c r="N86" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O86" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>28</v>
+      </c>
+      <c r="R86" t="s">
+        <v>31</v>
+      </c>
+      <c r="S86" s="4" t="str" cm="1">
+        <f t="array" ref="S86">INDEX(_xlfn.TEXTSPLIT($T86,{","," "}),1)</f>
+        <v>The Force Awakens</v>
+      </c>
+      <c r="T86" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="32.25">
+      <c r="A87" t="s">
+        <v>262</v>
+      </c>
+      <c r="B87" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" t="e">
         <f t="shared" si="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D87" t="e">
+        <f t="shared" si="8"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E87" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" t="e">
+        <f t="shared" si="9"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G87" s="4">
+        <f>IF(OR($E87="NA",$B87="NA"),0,$E87/($D87^2))</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="4">
+        <f t="shared" si="10"/>
         <v>-33.330065679835307</v>
       </c>
-      <c r="G83" s="4">
-        <f t="shared" si="8"/>
+      <c r="I87" s="4">
+        <f t="shared" si="11"/>
         <v>60</v>
       </c>
-      <c r="H83" t="s">
-        <v>52</v>
-      </c>
-      <c r="I83" t="s">
-        <v>102</v>
-      </c>
-      <c r="J83" t="s">
-        <v>102</v>
-      </c>
-      <c r="K83" t="s">
-        <v>25</v>
-      </c>
-      <c r="L83" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N83" t="s">
-        <v>25</v>
-      </c>
-      <c r="O83" t="s">
-        <v>22</v>
-      </c>
-      <c r="P83" s="4" t="str" cm="1">
-        <f t="array" ref="P83">INDEX(_xlfn.TEXTSPLIT($Q83,{","," "}),1)</f>
+      <c r="J87" t="s">
+        <v>67</v>
+      </c>
+      <c r="K87" t="s">
+        <v>67</v>
+      </c>
+      <c r="L87" t="s">
+        <v>67</v>
+      </c>
+      <c r="M87" t="s">
+        <v>28</v>
+      </c>
+      <c r="N87" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O87" t="e">
+        <f t="shared" si="13"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>28</v>
+      </c>
+      <c r="R87" t="s">
+        <v>28</v>
+      </c>
+      <c r="S87" s="4" t="str" cm="1">
+        <f t="array" ref="S87">INDEX(_xlfn.TEXTSPLIT($T87,{","," "}),1)</f>
         <v>The Force Awakens</v>
       </c>
-      <c r="Q83" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="32.25">
-      <c r="A84" t="s">
-        <v>256</v>
-      </c>
-      <c r="B84" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D84" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F84" s="4">
-        <f t="shared" si="7"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G84" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="H84" t="s">
-        <v>40</v>
-      </c>
-      <c r="I84" t="s">
-        <v>41</v>
-      </c>
-      <c r="J84" t="s">
-        <v>81</v>
-      </c>
-      <c r="K84" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N84" t="s">
-        <v>25</v>
-      </c>
-      <c r="O84" t="s">
-        <v>22</v>
-      </c>
-      <c r="P84" s="4" t="str" cm="1">
-        <f t="array" ref="P84">INDEX(_xlfn.TEXTSPLIT($Q84,{","," "}),1)</f>
-        <v>The Force Awakens</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="32.25">
-      <c r="A85" t="s">
-        <v>257</v>
-      </c>
-      <c r="B85" t="s">
-        <v>25</v>
-      </c>
-      <c r="C85" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D85" t="s">
-        <v>25</v>
-      </c>
-      <c r="E85" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F85" s="4">
-        <f t="shared" si="7"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G85" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="H85" t="s">
-        <v>40</v>
-      </c>
-      <c r="I85" t="s">
-        <v>41</v>
-      </c>
-      <c r="J85" t="s">
-        <v>40</v>
-      </c>
-      <c r="K85" t="s">
-        <v>25</v>
-      </c>
-      <c r="L85" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N85" t="s">
-        <v>25</v>
-      </c>
-      <c r="O85" t="s">
-        <v>22</v>
-      </c>
-      <c r="P85" s="4" t="str" cm="1">
-        <f t="array" ref="P85">INDEX(_xlfn.TEXTSPLIT($Q85,{","," "}),1)</f>
-        <v>The Force Awakens</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="32.25">
-      <c r="A86" t="s">
+      <c r="T87" t="s">
         <v>258</v>
       </c>
-      <c r="B86" t="s">
-        <v>25</v>
-      </c>
-      <c r="C86" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D86" t="s">
-        <v>25</v>
-      </c>
-      <c r="E86" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F86" s="4">
-        <f t="shared" si="7"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="H86" t="s">
-        <v>36</v>
-      </c>
-      <c r="I86" t="s">
-        <v>36</v>
-      </c>
-      <c r="J86" t="s">
-        <v>52</v>
-      </c>
-      <c r="K86" t="s">
-        <v>25</v>
-      </c>
-      <c r="L86" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N86" t="s">
-        <v>25</v>
-      </c>
-      <c r="O86" t="s">
-        <v>28</v>
-      </c>
-      <c r="P86" s="4" t="str" cm="1">
-        <f t="array" ref="P86">INDEX(_xlfn.TEXTSPLIT($Q86,{","," "}),1)</f>
-        <v>The Force Awakens</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="32.25">
-      <c r="A87" t="s">
-        <v>259</v>
-      </c>
-      <c r="B87" t="s">
-        <v>25</v>
-      </c>
-      <c r="C87" t="e">
-        <f t="shared" si="5"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D87" t="s">
-        <v>25</v>
-      </c>
-      <c r="E87" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F87" s="4">
-        <f t="shared" si="7"/>
-        <v>-33.330065679835307</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="H87" t="s">
-        <v>64</v>
-      </c>
-      <c r="I87" t="s">
-        <v>64</v>
-      </c>
-      <c r="J87" t="s">
-        <v>64</v>
-      </c>
-      <c r="K87" t="s">
-        <v>25</v>
-      </c>
-      <c r="L87" t="e">
-        <f t="shared" si="9"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N87" t="s">
-        <v>25</v>
-      </c>
-      <c r="O87" t="s">
-        <v>25</v>
-      </c>
-      <c r="P87" s="4" t="str" cm="1">
-        <f t="array" ref="P87">INDEX(_xlfn.TEXTSPLIT($Q87,{","," "}),1)</f>
-        <v>The Force Awakens</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="32.25">
+    </row>
+    <row r="88" spans="1:20" ht="32.25">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B88">
         <v>165</v>
       </c>
       <c r="C88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
+        <v>64.5</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="8"/>
         <v>1.65</v>
       </c>
-      <c r="D88">
+      <c r="E88">
         <v>45</v>
       </c>
-      <c r="E88" s="4">
-        <f t="shared" si="6"/>
+      <c r="F88">
+        <f t="shared" si="9"/>
+        <v>99</v>
+      </c>
+      <c r="G88" s="4">
+        <f>IF(OR($E88="NA",$B88="NA"),0,$E88/($D88^2))</f>
         <v>16.528925619834713</v>
       </c>
-      <c r="F88" s="4">
-        <f t="shared" si="7"/>
+      <c r="H88" s="4">
+        <f t="shared" si="10"/>
         <v>-16.801140060000595</v>
       </c>
-      <c r="G88" s="4">
-        <f t="shared" si="8"/>
+      <c r="I88" s="4">
+        <f t="shared" si="11"/>
         <v>55</v>
       </c>
-      <c r="H88" t="s">
-        <v>40</v>
-      </c>
-      <c r="I88" t="s">
-        <v>41</v>
-      </c>
       <c r="J88" t="s">
-        <v>40</v>
-      </c>
-      <c r="K88">
+        <v>43</v>
+      </c>
+      <c r="K88" t="s">
+        <v>44</v>
+      </c>
+      <c r="L88" t="s">
+        <v>43</v>
+      </c>
+      <c r="M88">
         <v>46</v>
       </c>
-      <c r="L88">
-        <f t="shared" si="9"/>
+      <c r="N88" t="b">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O88">
+        <f t="shared" si="13"/>
         <v>16790</v>
       </c>
-      <c r="N88" t="s">
-        <v>33</v>
-      </c>
-      <c r="O88" t="s">
-        <v>22</v>
-      </c>
-      <c r="P88" s="4" t="str" cm="1">
-        <f t="array" ref="P88">INDEX(_xlfn.TEXTSPLIT($Q88,{","," "}),1)</f>
+      <c r="Q88" t="s">
+        <v>36</v>
+      </c>
+      <c r="R88" t="s">
+        <v>25</v>
+      </c>
+      <c r="S88" s="4" t="str" cm="1">
+        <f t="array" ref="S88">INDEX(_xlfn.TEXTSPLIT($T88,{","," "}),1)</f>
         <v>Attack of the Clones</v>
       </c>
-      <c r="Q88" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17"/>
+      <c r="T88" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6781,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6789,71 +7933,71 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -6863,153 +8007,222 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C882684-D77A-4A87-900F-85966DA233B8}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="50.25" customHeight="1"/>
   <cols>
+    <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="70.875" customWidth="1"/>
     <col min="3" max="3" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1" t="s">
-        <v>273</v>
+    <row r="1" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A2" s="3">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="C2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="50.25" customHeight="1">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="C7" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B7" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="8" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A8" s="3">
-        <v>1</v>
+      <c r="A8" s="8" t="s">
+        <v>287</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A9">
-        <v>2</v>
+      <c r="A9" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A10">
-        <v>3</v>
+      <c r="A10" s="8" t="s">
+        <v>293</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C10" cm="1">
-        <f t="array" ref="C10">AVERAGE(_xlfn._xlws.FILTER(starwars!$E2:$E$88,starwars!$E2:$E$88&lt;&gt;0))</f>
+        <f t="array" ref="C10">AVERAGE(_xlfn._xlws.FILTER(starwars!$G2:$G$88,starwars!$G2:$G$88&lt;&gt;0))</f>
         <v>32.048638992833226</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A11">
-        <v>4</v>
+      <c r="A11" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A12">
-        <v>5</v>
+      <c r="A12" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="50.25" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>294</v>
+      <c r="A13" s="10" t="s">
+        <v>301</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>296</v>
-      </c>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="9" customFormat="1" ht="50.25" customHeight="1">
+      <c r="A14" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="101.25" customHeight="1">
+      <c r="A15" s="8" t="str" cm="1">
+        <f t="array" ref="A15">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
+        <v>1.</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="101.25" customHeight="1">
+      <c r="A16" s="8" t="str" cm="1">
+        <f t="array" ref="A16">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
+        <v>2.</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="101.25" customHeight="1">
+      <c r="A17" s="8" t="str" cm="1">
+        <f t="array" ref="A17">_xlfn.CONCAT(ROW()-ROW(chapter5),".")</f>
+        <v>3.</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:3" ht="50.25" customHeight="1">
+      <c r="B27" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
